--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>127.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>446.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.6%</t>
+          <t>-574.4%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.5%</t>
+          <t>-96.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.6%</t>
+          <t>-235.4%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.6%</t>
+          <t>-157.5%</t>
         </is>
       </c>
     </row>
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.413634851705366</v>
+        <v>-4.469126454666092</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211903793649282</v>
+        <v>1.189707152464991</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>-0.1002597578648048</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.917558303926293</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268962706605628</v>
+        <v>-4.324454309566355</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.279860754250617</v>
+        <v>1.257664113066326</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>0.04441238723493263</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>3.014449693547575</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328837533963321</v>
+        <v>-4.384329136924047</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241948314708966</v>
+        <v>1.219751673524675</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.01546244012275949</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>2.964562288534386</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.242038036184312</v>
+        <v>-4.297529639145038</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299068607143135</v>
+        <v>1.276871965958845</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.01546244012275949</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>2.986962781856952</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.244507742646118</v>
+        <v>-4.299999345606844</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298153125931825</v>
+        <v>1.275956484747534</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>-0.01793214658456566</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>2.98555335935328</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312877928970128</v>
+        <v>-4.368369531930854</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281811973876923</v>
+        <v>1.259615332692632</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.00865644754835071</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>3.002125701249711</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.191461499343651</v>
+        <v>-4.246953102304378</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.320815254359405</v>
+        <v>1.298618613175114</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.00865644754835071</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>2.992562409881602</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.222454658672357</v>
+        <v>-4.277946261633083</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.13312755566831</v>
+        <v>1.110930914484019</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.00865644754835071</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.817271974921989</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.046980398879887</v>
+        <v>-4.102472001840614</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.207884491577085</v>
+        <v>1.185687850392795</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.00865644754835071</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.821839206913777</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.157916651521136</v>
+        <v>-4.213408254481863</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.139252019281793</v>
+        <v>1.117055378097502</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.00865644754835071</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.797581235674984</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.360943229064369</v>
+        <v>-4.416434832025096</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.061172773484405</v>
+        <v>1.038976132300114</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.2116830250915841</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.67889667436895</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.203017630129076</v>
+        <v>-4.258509233089803</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134515399490654</v>
+        <v>1.112318758306364</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.2116830250915841</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.689069060801082</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.116774167102698</v>
+        <v>-4.172265770063425</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.163959055275066</v>
+        <v>1.141762414090775</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.2116830250915841</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.684015331374942</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.11795725175376</v>
+        <v>-4.173448854714486</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.155261596859167</v>
+        <v>1.133064955674876</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.2173260735580956</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.672405277739561</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.994829544759677</v>
+        <v>-4.050321147720403</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.205064552689902</v>
+        <v>1.182867911505611</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.2173260735580956</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.672957150772663</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.902019063308817</v>
+        <v>-3.957510666269544</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.171461437161611</v>
+        <v>1.14926479597732</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.1245155921072363</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.657916131534544</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.853456011087787</v>
+        <v>-3.908947614048514</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.192760133974624</v>
+        <v>1.170563492790333</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>-0.07595253988620609</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.688927438791763</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.740784792851537</v>
+        <v>-3.796276395812264</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.232904329780847</v>
+        <v>1.210707688596556</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.03671867835004411</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.751605878245236</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.628407791668864</v>
+        <v>-3.683899394629591</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.283346426084583</v>
+        <v>1.261149784900293</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.03671867835004411</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.757097174075903</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.826642360555595</v>
+        <v>-3.882133963516321</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.21554980029843</v>
+        <v>1.19335315911414</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.1615158905366865</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.649653634512404</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.909643641580874</v>
+        <v>-3.9651352445416</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.020705007888972</v>
+        <v>0.9985083667046812</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.1800867750638602</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.476866823796753</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.750449369524298</v>
+        <v>-3.805940972485024</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.204532377430808</v>
+        <v>1.182335736246517</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.1800867750638602</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.597016484515958</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.8370479525054</v>
+        <v>-3.892539555466127</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.18440597034069</v>
+        <v>1.162209329156399</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.1800867750638602</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.611529510618281</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.798664289947249</v>
+        <v>-3.854155892907976</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.197178876706319</v>
+        <v>1.174982235522028</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.1417031125057091</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.631979149495541</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.621547959912083</v>
+        <v>-3.67703956287281</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.264754437565687</v>
+        <v>1.242557796381397</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.1417031125057091</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.628708178340843</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.59184583593579</v>
+        <v>-3.647337438896516</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.277318678918118</v>
+        <v>1.255122037733827</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.1461732377210224</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.626709494973568</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.412470414697022</v>
+        <v>-3.467962017657748</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.34285582272004</v>
+        <v>1.320659181535749</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>0.01060352044969626</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.714562525182413</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.457484628217628</v>
+        <v>-3.512976231178354</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.305657592643387</v>
+        <v>1.283460951459096</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>-0.01974537486490835</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.67716064332524</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.724489138490063</v>
+        <v>-3.77998074145079</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.204547350873358</v>
+        <v>1.182350709689068</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.2141084129078569</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.566234382838417</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.013276358948978</v>
+        <v>-4.068767961909705</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.088236384586294</v>
+        <v>1.066039743402003</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.3151945330068573</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.504786632675518</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.980800772778206</v>
+        <v>-4.036292375738933</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098826580608919</v>
+        <v>1.076629939424629</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.3151945330068573</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.502386594229835</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.961762645070909</v>
+        <v>-4.017254248031636</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102966550900083</v>
+        <v>1.080769909715793</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3733781443380518</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.464001146639363</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.978508510327284</v>
+        <v>-4.034000113288011</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.273850073736214</v>
+        <v>1.251653432551923</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3733781443380518</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.641583015578044</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.030828890928076</v>
+        <v>-4.086320493888802</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.25375525048203</v>
+        <v>1.23155860929774</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3384312843291797</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.663384460569501</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.175151796852995</v>
+        <v>-4.230643399813721</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.202034618508989</v>
+        <v>1.179837977324698</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3384312843291797</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.669392990966426</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.027408826617992</v>
+        <v>-4.082900429578719</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.340284454395012</v>
+        <v>1.318087813210721</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1706239270942965</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.849230053099378</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.129423509149214</v>
+        <v>-4.18491511210994</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.302272202914004</v>
+        <v>1.280075561729713</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1706239270942965</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.852023674630859</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.992814165055121</v>
+        <v>-4.048305768015847</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.357578288943299</v>
+        <v>1.335381647759009</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>-0.03401458300020405</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>2.934651629478973</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.857129448798661</v>
+        <v>3.581605779076075</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.130149935872927</v>
+        <v>-4.128431728095578</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.301724457356287</v>
+        <v>1.302411740467227</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1158587508572834</v>
+        <v>-0.1141405430799342</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.884625605504836</v>
+        <v>2.885656530171245</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.6%</t>
+          <t>446.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.4%</t>
+          <t>-583.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-246.0%</t>
+          <t>-249.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-96.0%</t>
+          <t>-209.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.4%</t>
+          <t>-231.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.5%</t>
+          <t>-155.1%</t>
         </is>
       </c>
     </row>
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.469126454666092</v>
+        <v>-4.413634851705366</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.189707152464991</v>
+        <v>1.211903793649282</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1002597578648048</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.917558303926293</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.324454309566355</v>
+        <v>-4.268962706605628</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.257664113066326</v>
+        <v>1.279860754250617</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.04441238723493263</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.014449693547575</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.384329136924047</v>
+        <v>-4.328837533963321</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.219751673524675</v>
+        <v>1.241948314708966</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.01546244012275949</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.964562288534386</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.297529639145038</v>
+        <v>-4.242038036184312</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.276871965958845</v>
+        <v>1.299068607143135</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.01546244012275949</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.986962781856952</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.299999345606844</v>
+        <v>-4.244507742646118</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.275956484747534</v>
+        <v>1.298153125931825</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.01793214658456566</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.98555335935328</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.368369531930854</v>
+        <v>-4.312877928970128</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.259615332692632</v>
+        <v>1.281811973876923</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.00865644754835071</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.002125701249711</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.246953102304378</v>
+        <v>-4.191461499343651</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.298618613175114</v>
+        <v>1.320815254359405</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.00865644754835071</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.992562409881602</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.277946261633083</v>
+        <v>-4.222454658672357</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.110930914484019</v>
+        <v>1.13312755566831</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.00865644754835071</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.817271974921989</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.102472001840614</v>
+        <v>-4.046980398879887</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.185687850392795</v>
+        <v>1.207884491577085</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.00865644754835071</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.821839206913777</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.213408254481863</v>
+        <v>-4.157916651521136</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.117055378097502</v>
+        <v>1.139252019281793</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.00865644754835071</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.797581235674984</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.416434832025096</v>
+        <v>-4.360943229064369</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.038976132300114</v>
+        <v>1.061172773484405</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2116830250915841</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.67889667436895</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.258509233089803</v>
+        <v>-4.203017630129076</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.112318758306364</v>
+        <v>1.134515399490654</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2116830250915841</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.689069060801082</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.172265770063425</v>
+        <v>-4.164828684458985</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.141762414090775</v>
+        <v>1.144737248332552</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2116830250915841</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.684015331374942</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.173448854714486</v>
+        <v>-4.166011769110046</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.133064955674876</v>
+        <v>1.136039789916652</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2173260735580956</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.672405277739561</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.050321147720403</v>
+        <v>-4.042884062115963</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.182867911505611</v>
+        <v>1.185842745747387</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2173260735580956</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.672957150772663</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.957510666269544</v>
+        <v>-3.950073580665104</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.14926479597732</v>
+        <v>1.152239630219096</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1245155921072363</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.657916131534544</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.908947614048514</v>
+        <v>-3.901510528444073</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.170563492790333</v>
+        <v>1.17353832703211</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.07595253988620609</v>
+        <v>-0.02046093692547968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.688927438791763</v>
+        <v>2.722222400568199</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.796276395812264</v>
+        <v>-3.788839310207823</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.210707688596556</v>
+        <v>1.213682522838333</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.03671867835004411</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.751605878245236</v>
+        <v>2.784900840021672</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.683899394629591</v>
+        <v>-3.676462309025151</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.261149784900293</v>
+        <v>1.264124619142069</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.03671867835004411</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.757097174075903</v>
+        <v>2.790392135852339</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.882133963516321</v>
+        <v>-3.874696877911881</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.19335315911414</v>
+        <v>1.196327993355916</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1615158905366865</v>
+        <v>-0.1060242875759601</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.649653634512404</v>
+        <v>2.68294859628884</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.9651352445416</v>
+        <v>-3.95769815893716</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9985083667046812</v>
+        <v>1.001483200946457</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1800867750638602</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.476866823796753</v>
+        <v>2.510161785573189</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.805940972485024</v>
+        <v>-3.798503886880584</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.182335736246517</v>
+        <v>1.185310570488294</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1800867750638602</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.597016484515958</v>
+        <v>2.630311446292394</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.892539555466127</v>
+        <v>-3.885102469861687</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.162209329156399</v>
+        <v>1.165184163398175</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1800867750638602</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.611529510618281</v>
+        <v>2.644824472394717</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.854155892907976</v>
+        <v>-3.846718807303536</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.174982235522028</v>
+        <v>1.177957069763804</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1417031125057091</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.631979149495541</v>
+        <v>2.665274111271977</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.67703956287281</v>
+        <v>-3.66960247726837</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.242557796381397</v>
+        <v>1.245532630623173</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1417031125057091</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.628708178340843</v>
+        <v>2.662003140117279</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.647337438896516</v>
+        <v>-3.639900353292076</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.255122037733827</v>
+        <v>1.258096871975603</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1461732377210224</v>
+        <v>-0.090681634760296</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.626709494973568</v>
+        <v>2.660004456750004</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.467962017657748</v>
+        <v>-3.460524932053308</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.320659181535749</v>
+        <v>1.323634015777525</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.01060352044969626</v>
+        <v>0.06609512341042267</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.714562525182413</v>
+        <v>2.747857486958849</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.512976231178354</v>
+        <v>-3.505539145573914</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.283460951459096</v>
+        <v>1.286435785700872</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.01974537486490835</v>
+        <v>0.03574622809581807</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.67716064332524</v>
+        <v>2.710455605101676</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.77998074145079</v>
+        <v>-3.772543655846349</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.182350709689068</v>
+        <v>1.185325543930844</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2141084129078569</v>
+        <v>-0.1586168099471305</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.566234382838417</v>
+        <v>2.599529344614853</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.068767961909705</v>
+        <v>-4.061330876305265</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.066039743402003</v>
+        <v>1.069014577643779</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3151945330068573</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.504786632675518</v>
+        <v>2.538081594451954</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.036292375738933</v>
+        <v>-4.112167096637007</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.076629939424629</v>
+        <v>1.046280051065399</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3151945330068573</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.502386594229835</v>
+        <v>2.535681556006271</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.017254248031636</v>
+        <v>-4.09312896892971</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.080769909715793</v>
+        <v>1.050420021356563</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3733781443380518</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.464001146639363</v>
+        <v>2.497296108415799</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.034000113288011</v>
+        <v>-4.109874834186085</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.251653432551923</v>
+        <v>1.221303544192693</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3733781443380518</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.641583015578044</v>
+        <v>2.67487797735448</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.086320493888802</v>
+        <v>-4.162195214786877</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.23155860929774</v>
+        <v>1.20120872093851</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3384312843291797</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.663384460569501</v>
+        <v>2.696679422345936</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.230643399813721</v>
+        <v>-4.306518120711796</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.179837977324698</v>
+        <v>1.149488088965468</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3384312843291797</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.669392990966426</v>
+        <v>2.702687952742862</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.082900429578719</v>
+        <v>-4.158775150476793</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.318087813210721</v>
+        <v>1.287737924851491</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1706239270942965</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.849230053099378</v>
+        <v>2.882525014875814</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.18491511210994</v>
+        <v>-4.260789833008015</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.280075561729713</v>
+        <v>1.249725673370484</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1706239270942965</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.852023674630859</v>
+        <v>2.885318636407295</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.048305768015847</v>
+        <v>-4.124180488913922</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.335381647759009</v>
+        <v>1.305031759399779</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.03401458300020405</v>
+        <v>0.02147701996052237</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.934651629478973</v>
+        <v>2.967946591255409</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.581605779076075</v>
+        <v>3.574438017181668</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.128431728095578</v>
+        <v>-4.220271289110777</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.302411740467227</v>
+        <v>1.265675916061147</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1141405430799342</v>
+        <v>-0.07461378023633336</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.885656530171245</v>
+        <v>2.909372587877406</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.6%</t>
+          <t>-583.2%</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-249.7%</t>
+          <t>-249.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.5%</t>
+          <t>-236.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-157.9%</t>
         </is>
       </c>
     </row>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.164828684458985</v>
+        <v>-4.116774167102698</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.144737248332552</v>
+        <v>1.163959055275066</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1561914221308577</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.166011769110046</v>
+        <v>-4.11795725175376</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.136039789916652</v>
+        <v>1.155261596859167</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1618344705973692</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.042884062115963</v>
+        <v>-3.994829544759677</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.185842745747387</v>
+        <v>1.205064552689902</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1618344705973692</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.950073580665104</v>
+        <v>-3.902019063308817</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.152239630219096</v>
+        <v>1.171461437161611</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.06902398914650987</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.901510528444073</v>
+        <v>-3.853456011087787</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.17353832703211</v>
+        <v>1.192760133974624</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.02046093692547968</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.788839310207823</v>
+        <v>-3.740784792851537</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.213682522838333</v>
+        <v>1.232904329780847</v>
       </c>
       <c r="F1948" t="n">
         <v>0.09221028131077053</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.676462309025151</v>
+        <v>-3.628407791668864</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.264124619142069</v>
+        <v>1.283346426084583</v>
       </c>
       <c r="F1949" t="n">
         <v>0.09221028131077053</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.874696877911881</v>
+        <v>-3.826642360555595</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.196327993355916</v>
+        <v>1.21554980029843</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1060242875759601</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.95769815893716</v>
+        <v>-3.909643641580874</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.001483200946457</v>
+        <v>1.020705007888972</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1245951721031338</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.798503886880584</v>
+        <v>-3.750449369524298</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.185310570488294</v>
+        <v>1.204532377430808</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1245951721031338</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.885102469861687</v>
+        <v>-3.8370479525054</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.165184163398175</v>
+        <v>1.18440597034069</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1245951721031338</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.846718807303536</v>
+        <v>-3.798664289947249</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.177957069763804</v>
+        <v>1.197178876706319</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.08621150954498263</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.66960247726837</v>
+        <v>-3.621547959912083</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.245532630623173</v>
+        <v>1.264754437565687</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.08621150954498263</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.639900353292076</v>
+        <v>-3.59184583593579</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.258096871975603</v>
+        <v>1.277318678918118</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.090681634760296</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.460524932053308</v>
+        <v>-3.412470414697022</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.323634015777525</v>
+        <v>1.34285582272004</v>
       </c>
       <c r="F1957" t="n">
         <v>0.06609512341042267</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.505539145573914</v>
+        <v>-3.457484628217628</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.286435785700872</v>
+        <v>1.305657592643387</v>
       </c>
       <c r="F1958" t="n">
         <v>0.03574622809581807</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.772543655846349</v>
+        <v>-3.724489138490063</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.185325543930844</v>
+        <v>1.204547350873358</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1586168099471305</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.061330876305265</v>
+        <v>-4.013276358948978</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.069014577643779</v>
+        <v>1.088236384586294</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2597029300461309</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.112167096637007</v>
+        <v>-4.061208420577461</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.046280051065399</v>
+        <v>1.066663521489217</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2597029300461309</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.09312896892971</v>
+        <v>-4.042170292870164</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.050420021356563</v>
+        <v>1.070803491780381</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3178865413773254</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.109874834186085</v>
+        <v>-4.058916158126539</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.221303544192693</v>
+        <v>1.241687014616512</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3178865413773254</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.162195214786877</v>
+        <v>-4.111236538727331</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.20120872093851</v>
+        <v>1.221592191362328</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2829396813684533</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.306518120711796</v>
+        <v>-4.25555944465225</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.149488088965468</v>
+        <v>1.169871559389287</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2829396813684533</v>
@@ -46769,10 +46769,10 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.158775150476793</v>
+        <v>-4.107816474417247</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.287737924851491</v>
+        <v>1.30812139527531</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1151323241335701</v>
@@ -46792,10 +46792,10 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.260789833008015</v>
+        <v>-4.209831156948469</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.249725673370484</v>
+        <v>1.270109143794302</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1151323241335701</v>
@@ -46815,10 +46815,10 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.124180488913922</v>
+        <v>-4.073221812854376</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.305031759399779</v>
+        <v>1.325415229823597</v>
       </c>
       <c r="F1968" t="n">
         <v>0.02147701996052237</v>
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.220271289110777</v>
+        <v>-4.215987145677026</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.265675916061147</v>
+        <v>1.267389573434648</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.07461378023633336</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.909372587877406</v>
+        <v>2.881367868301929</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.2%</t>
+          <t>448.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.2%</t>
+          <t>-582.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-249.5%</t>
+          <t>-249.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-209.2%</t>
+          <t>-208.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.1%</t>
+          <t>-235.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.9%</t>
+          <t>-150.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1969"/>
+  <dimension ref="A1:G1970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.326342950368402</v>
+        <v>-7.321385619058083</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02513624506076884</v>
+        <v>0.02711917758489601</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.310011780626476</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.170022781145991</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.282794543597712</v>
+        <v>-7.277837212287393</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03559499567395186</v>
+        <v>0.03757792819807904</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.310011780626476</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.163062169050898</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.040646150143854</v>
+        <v>-7.035688818833535</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1469167074366382</v>
+        <v>0.1488996399607654</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.310011780626476</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.177524523432041</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.977416778375505</v>
+        <v>-6.972459447065186</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1667405766031722</v>
+        <v>0.1687235091272998</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.310011780626476</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.172056643891236</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.854125643558374</v>
+        <v>-6.849168312248056</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2135551245406018</v>
+        <v>0.2155380570647289</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.186720645809346</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.243529418792091</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.832976444654931</v>
+        <v>-6.828019113344612</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2297157823393041</v>
+        <v>0.2316987148634317</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.165571446905902</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.263919916371483</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.589211002671487</v>
+        <v>-6.584253671361168</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3230026674797326</v>
+        <v>0.3249856000038602</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.165571446905902</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.259700624718533</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.442313974953617</v>
+        <v>-6.437356643643298</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3838857924868964</v>
+        <v>0.385868725011024</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.117913204927314</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.290419883825702</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.192463581004542</v>
+        <v>-6.187506249694223</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4765680250502284</v>
+        <v>0.4785509575743561</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.117913204927314</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.283161958809405</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01657148853711</v>
+        <v>-6.011614157226791</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5505239855578501</v>
+        <v>0.5525069180819777</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.117913204927314</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.286761082330053</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.845125025514647</v>
+        <v>-5.840167694204328</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6324300768213891</v>
+        <v>0.6344130093455167</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-0.9464667419048512</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.402956466198085</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.620092025845824</v>
+        <v>-5.615134694535505</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7214637543052151</v>
+        <v>0.7234466868293428</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.7214337422360284</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.536996743615676</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.556456283611889</v>
+        <v>-5.551498952301571</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7516128522531065</v>
+        <v>0.7535957847772341</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.6577980000020939</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.579872990010353</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.463456242405991</v>
+        <v>-5.458498911095672</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7700071275192615</v>
+        <v>0.7719900600433887</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.6577980000020939</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.561067248794149</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.223025745601131</v>
+        <v>-5.218068414290812</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8679224028660828</v>
+        <v>0.8699053353902104</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.4173675031972336</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.707068623501943</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.150783177429936</v>
+        <v>-5.145825846119617</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9007487439693809</v>
+        <v>0.9027316764935085</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.4173675031972336</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.710997937336763</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034843327804751</v>
+        <v>-5.029885996494432</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9478032677367949</v>
+        <v>0.9497862002609225</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.3405457721811097</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.757769559863777</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.926038442325024</v>
+        <v>-4.921081111014705</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9883232931486794</v>
+        <v>0.9903062256728068</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.3405457721811097</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.754767631083771</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.706017644288013</v>
+        <v>-4.701060312977694</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077910649374098</v>
+        <v>1.079893581898225</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1993259271131295</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.841078575135173</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.573149955224736</v>
+        <v>-4.568192623914417</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146951907801232</v>
+        <v>1.14893484032536</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.1993259271131295</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.856972757936996</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.413634851705366</v>
+        <v>-4.408677520395047</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211903793649282</v>
+        <v>1.213886726173409</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>-0.03981082359375954</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.95382766448892</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268962706605628</v>
+        <v>-4.26400537529531</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.279860754250617</v>
+        <v>1.281843686774744</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>0.1048613215059779</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>3.050719054110202</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328837533963321</v>
+        <v>-4.323880202653002</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241948314708966</v>
+        <v>1.243931247233093</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.04498649414828576</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>3.000831649097013</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.242038036184312</v>
+        <v>-4.237080704873993</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299068607143135</v>
+        <v>1.301051539667263</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.04498649414828576</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>3.023232142419579</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.244507742646118</v>
+        <v>-4.239550411335799</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298153125931825</v>
+        <v>1.300136058455953</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>0.0425167876864796</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>3.021822719915908</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312877928970128</v>
+        <v>-4.307920597659809</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281811973876923</v>
+        <v>1.283794906401051</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.05179248672269454</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>3.038395061812338</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.191461499343651</v>
+        <v>-4.186504168033332</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.320815254359405</v>
+        <v>1.322798186883532</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.05179248672269454</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>3.02883177044423</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.222454658672357</v>
+        <v>-4.217497327362038</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.13312755566831</v>
+        <v>1.135110488192437</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.05179248672269454</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.853541335484616</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.046980398879887</v>
+        <v>-4.042023067569568</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.207884491577085</v>
+        <v>1.209867424101213</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.05179248672269454</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.858108567476404</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.157916651521136</v>
+        <v>-4.152959320210817</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.139252019281793</v>
+        <v>1.14123495180592</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.05179248672269454</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.833850596237611</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.360943229064369</v>
+        <v>-4.35598589775405</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.061172773484405</v>
+        <v>1.063155706008533</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.1512340908205388</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.715166034931577</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.203017630129076</v>
+        <v>-4.198060298818757</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134515399490654</v>
+        <v>1.136498332014782</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.1512340908205388</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.725338421363709</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.116774167102698</v>
+        <v>-4.111816835792379</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.163959055275066</v>
+        <v>1.165941987799193</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.1512340908205388</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.720284691937569</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.11795725175376</v>
+        <v>-4.112999920443441</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.155261596859167</v>
+        <v>1.157244529383294</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.1568771392870504</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.708674638302188</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.994829544759677</v>
+        <v>-3.989872213449358</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.205064552689902</v>
+        <v>1.207047485214029</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.1568771392870504</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.70922651133529</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.902019063308817</v>
+        <v>-3.897061731998499</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.171461437161611</v>
+        <v>1.173444369685739</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.06406665783619103</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.694185492097171</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.853456011087787</v>
+        <v>-3.848498679777468</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.192760133974624</v>
+        <v>1.194743066498752</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>-0.01550360561516084</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.72519679935439</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.740784792851537</v>
+        <v>-3.735827461541218</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.232904329780847</v>
+        <v>1.234887262304975</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.09716761262108936</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.787875238807863</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.628407791668864</v>
+        <v>-3.623450460358546</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.283346426084583</v>
+        <v>1.285329358608711</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.09716761262108936</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.79336653463853</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.826642360555595</v>
+        <v>-3.821685029245276</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.21554980029843</v>
+        <v>1.217532732822558</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.1010669562656412</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.685922995075031</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.909643641580874</v>
+        <v>-3.904686310270555</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.020705007888972</v>
+        <v>1.0226879404131</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.119637840792815</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.51313618435938</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.750449369524298</v>
+        <v>-3.745492038213979</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.204532377430808</v>
+        <v>1.206515309954935</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.119637840792815</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.633285845078586</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.8370479525054</v>
+        <v>-3.832090621195082</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.18440597034069</v>
+        <v>1.186388902864817</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.119637840792815</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.647798871180909</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.798664289947249</v>
+        <v>-3.793706958636931</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.197178876706319</v>
+        <v>1.199161809230447</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.0812541782346638</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.668248510058168</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.621547959912083</v>
+        <v>-3.616590628601764</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.264754437565687</v>
+        <v>1.266737370089815</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.0812541782346638</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.66497753890347</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.59184583593579</v>
+        <v>-3.586888504625471</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.277318678918118</v>
+        <v>1.279301611442246</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.08572430344997717</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.662978855536195</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.412470414697022</v>
+        <v>-3.407513083386703</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.34285582272004</v>
+        <v>1.344838755244167</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>0.07105245472074151</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.750831885745041</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.457484628217628</v>
+        <v>-3.452527296907309</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.305657592643387</v>
+        <v>1.307640525167514</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>0.0407035594061369</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.713430003887868</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.724489138490063</v>
+        <v>-3.719531807179744</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.204547350873358</v>
+        <v>1.206530283397486</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.1536594786368117</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.602503743401044</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.013276358948978</v>
+        <v>-4.00831902763866</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.088236384586294</v>
+        <v>1.090219317110421</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.254745598735812</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.541055993238145</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.061208420577461</v>
+        <v>-4.056251089267143</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.066663521489217</v>
+        <v>1.068646454013345</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.254745598735812</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.538655954792462</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.042170292870164</v>
+        <v>-4.037212961559845</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.070803491780381</v>
+        <v>1.072786424304509</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3129292100670066</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.50027050720199</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.058916158126539</v>
+        <v>-4.053958826816221</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.241687014616512</v>
+        <v>1.243669947140639</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3129292100670066</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.677852376140671</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.111236538727331</v>
+        <v>-4.106279207417012</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.221592191362328</v>
+        <v>1.223575123886456</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.2779823500581344</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.699653821132128</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.25555944465225</v>
+        <v>-4.250602113341931</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.169871559389287</v>
+        <v>1.171854491913414</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.2779823500581344</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.705662351529054</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.107816474417247</v>
+        <v>-4.102859143106929</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.30812139527531</v>
+        <v>1.310104327799437</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1101749928232513</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.885499413662005</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.209831156948469</v>
+        <v>-4.20487382563815</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.270109143794302</v>
+        <v>1.27209207631843</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1101749928232513</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.888293035193486</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.073221812854376</v>
+        <v>-4.068264481544057</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.325415229823597</v>
+        <v>1.327398162347725</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>0.02643435127084121</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>2.9709209900416</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,45 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.574438017181668</v>
+        <v>3.798236219360613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.215987145677026</v>
+        <v>-4.211029814366707</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.267389573434648</v>
+        <v>1.269372505958775</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.1163309815518092</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.881367868301929</v>
+        <v>2.88434226708812</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="2" t="n">
+        <v>45432</v>
+      </c>
+      <c r="B1970" t="n">
+        <v>3.794318571407198</v>
+      </c>
+      <c r="C1970" t="n">
+        <v>2.965788990868945</v>
+      </c>
+      <c r="D1970" t="n">
+        <v>-4.211029814366707</v>
+      </c>
+      <c r="E1970" t="n">
+        <v>1.269372505958775</v>
+      </c>
+      <c r="F1970" t="n">
+        <v>-0.1163309815518092</v>
+      </c>
+      <c r="G1970" t="n">
+        <v>2.958852787855313</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>448.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.7%</t>
+          <t>-562.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-249.3%</t>
+          <t>-241.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-208.8%</t>
+          <t>-192.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.6%</t>
+          <t>-232.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.1%</t>
+          <t>-141.3%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355691</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386097</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998565</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082129</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.976706868804879</v>
+        <v>-9.853637720539343</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8491300814175879</v>
+        <v>-0.7999024221113737</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.165457029933451</v>
+        <v>-2.129372078375717</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.842634872458041</v>
+        <v>1.864285843392681</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.90323703713743</v>
+        <v>-9.780167888871894</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8043704472571873</v>
+        <v>-0.7551427879509731</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.091987198266002</v>
+        <v>-2.055902246708268</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.902088472951931</v>
+        <v>1.923739443886571</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07836145452397</v>
+        <v>-9.955292306258437</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8598649934642877</v>
+        <v>-0.8106373341580735</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.231026664094812</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.811569043267521</v>
+        <v>1.833220014202162</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31281354853846</v>
+        <v>-10.18974440027293</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9608649959716797</v>
+        <v>-0.9116373366654655</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.231026664094812</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.804349878365925</v>
+        <v>1.826000849300566</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.6006173930757</v>
+        <v>-10.47754824481017</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.082658724560551</v>
+        <v>-1.033431065254337</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.554915460189784</v>
+        <v>-2.51883050863205</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.624995380869606</v>
+        <v>1.646646351804247</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.65340354867603</v>
+        <v>-10.53033440041049</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.102657396962126</v>
+        <v>-1.053429737655911</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.650590946772181</v>
+        <v>-2.614505995214447</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.568705878758724</v>
+        <v>1.590356849693365</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.88543246841229</v>
+        <v>-10.76236332014675</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.192775236227515</v>
+        <v>-1.143547576921301</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.67651869240287</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.534191989074785</v>
+        <v>1.555842960009426</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.83341695444348</v>
+        <v>-10.71034780617794</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.16797869495359</v>
+        <v>-1.118751035647375</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.67651869240287</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.538182324761186</v>
+        <v>1.559833295695827</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.9750887961676</v>
+        <v>-10.85201964790206</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.226122658541979</v>
+        <v>-1.176894999235765</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.67651869240287</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.536707097862444</v>
+        <v>1.558358068797085</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.92549795174276</v>
+        <v>-10.80242880347723</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.191232910607174</v>
+        <v>-1.142005251300959</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.663012799535771</v>
+        <v>-2.626927847978036</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.581515014682217</v>
+        <v>1.603165985616857</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.72634584450566</v>
+        <v>-10.60327669624013</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.124623201359017</v>
+        <v>-1.075395542052803</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.461605322028223</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.689308367540062</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.50050069178625</v>
+        <v>-10.37743154352072</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.024706067235044</v>
+        <v>-0.9754784079288297</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.41967864644106</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.724043445928569</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.37592203544866</v>
+        <v>-10.25285288718313</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9737354601439487</v>
+        <v>-0.9245078008377345</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.41967864644106</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.725182590484628</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.42881732349295</v>
+        <v>-10.30574817522741</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9922598011995554</v>
+        <v>-0.9430321418933412</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.414723300352613</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.730789572299803</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.1449085925642</v>
+        <v>-10.02183944429866</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8729626045894197</v>
+        <v>-0.8237349452832055</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.414723300352613</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.73652327653844</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.07354219995455</v>
+        <v>-9.950473051689016</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8541533099394254</v>
+        <v>-0.8049256506332112</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.343356907742966</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.769605849710363</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.809705332750482</v>
+        <v>-9.686636184484946</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7585020443707053</v>
+        <v>-0.7092743850644911</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.343356907742966</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.759722368397456</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.542463531882085</v>
+        <v>-9.419394383616549</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6534398845227201</v>
+        <v>-0.6042122252165059</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.343356907742966</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.757887807898082</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.444556493205594</v>
+        <v>-9.321487344940058</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6145773840255848</v>
+        <v>-0.5653497247193702</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.275371157882409</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.798378942840955</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.420602952229636</v>
+        <v>-9.2975338039641</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6043274614897078</v>
+        <v>-0.5550998021834936</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.251417616906452</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.813419573572023</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.156543013906839</v>
+        <v>-9.033473865641303</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5119638023223412</v>
+        <v>-0.462736143016127</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.987357678583656</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.958595220403949</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.449463390402002</v>
+        <v>-8.326394242136466</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2319189865807072</v>
+        <v>-0.182691327274493</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-1.987357678583656</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.955808186743648</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.409279092035812</v>
+        <v>-8.286209943770276</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2155016433463897</v>
+        <v>-0.1662739840401755</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-1.947173380217465</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.980262389651203</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.329209296498007</v>
+        <v>-8.206140148232471</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1841069039105108</v>
+        <v>-0.1348792446042966</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-1.867103584679661</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>2.027671088194643</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.095728074268408</v>
+        <v>-7.972658926002873</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08278998618081879</v>
+        <v>-0.03356232687460459</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.633622362450062</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.175684250370255</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.946061683260893</v>
+        <v>-7.822992534995358</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02581564009077209</v>
+        <v>0.02341201921544211</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.540718871207526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.228534134802817</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.813786209630006</v>
+        <v>-7.690717061364471</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02246203610860986</v>
+        <v>0.07168969541482362</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.40844339757664</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.303266905728376</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.623186534956853</v>
+        <v>-7.500117386691318</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1015169666655074</v>
+        <v>0.1507446259717216</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.217843722903487</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.420441771219904</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.374186736273272</v>
+        <v>-7.251117588007737</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2140232273625986</v>
+        <v>0.2632508866688128</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.217843722903487</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.433348112443563</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.479776726046377</v>
+        <v>-7.356707577780842</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04381130185413795</v>
+        <v>0.09303896116035215</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.323433712676591</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.242018188980482</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.498511628164974</v>
+        <v>-7.375442479899439</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08486168288378559</v>
+        <v>0.1340893421899998</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.323433712676591</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.290562530857568</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350571586757375</v>
+        <v>-7.22750243849184</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02415877675865774</v>
+        <v>0.07338643606487194</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.303112796768034</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.182876157714535</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.321385619058083</v>
+        <v>-7.203273802102867</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02711917758489601</v>
+        <v>0.07436390436698259</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.310011780626476</v>
+        <v>-1.278884160379061</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.170022781145991</v>
+        <v>2.188699353294441</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.277837212287393</v>
+        <v>-7.159725395332177</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03757792819807904</v>
+        <v>0.08482265498016561</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.310011780626476</v>
+        <v>-1.278884160379061</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.163062169050898</v>
+        <v>2.181738741199347</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.035688818833535</v>
+        <v>-6.917577001878318</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1488996399607654</v>
+        <v>0.196144366742852</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.310011780626476</v>
+        <v>-1.278884160379061</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.177524523432041</v>
+        <v>2.19620109558049</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.972459447065186</v>
+        <v>-6.85434763010997</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1687235091272998</v>
+        <v>0.2159682359093864</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.310011780626476</v>
+        <v>-1.278884160379061</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.172056643891236</v>
+        <v>2.190733216039686</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.849168312248056</v>
+        <v>-6.731056495292839</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2155380570647289</v>
+        <v>0.2627827838468155</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.186720645809346</v>
+        <v>-1.155593025561931</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.243529418792091</v>
+        <v>2.262205990940541</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.828019113344612</v>
+        <v>-6.709907296389396</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2316987148634317</v>
+        <v>0.2789434416455183</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.165571446905902</v>
+        <v>-1.134443826658488</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.263919916371483</v>
+        <v>2.282596488519932</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.584253671361168</v>
+        <v>-6.466141854405952</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3249856000038602</v>
+        <v>0.3722303267859464</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.165571446905902</v>
+        <v>-1.134443826658488</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.259700624718533</v>
+        <v>2.278377196866982</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.437356643643298</v>
+        <v>-6.319244826688081</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.385868725011024</v>
+        <v>0.433113451793111</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.117913204927314</v>
+        <v>-1.086785584679899</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.290419883825702</v>
+        <v>2.309096455974151</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.187506249694223</v>
+        <v>-6.069394432739006</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4785509575743561</v>
+        <v>0.5257956843564426</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.117913204927314</v>
+        <v>-1.086785584679899</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.283161958809405</v>
+        <v>2.301838530957853</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.011614157226791</v>
+        <v>-5.893502340271574</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5525069180819777</v>
+        <v>0.5997516448640643</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.117913204927314</v>
+        <v>-1.086785584679899</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.286761082330053</v>
+        <v>2.305437654478502</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.840167694204328</v>
+        <v>-5.722055877249111</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6344130093455167</v>
+        <v>0.6816577361276037</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9464667419048512</v>
+        <v>-0.9153391216574364</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.402956466198085</v>
+        <v>2.421633038346534</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.615134694535505</v>
+        <v>-5.497022877580288</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7234466868293428</v>
+        <v>0.7706914136114298</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7214337422360284</v>
+        <v>-0.6903061219886135</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.536996743615676</v>
+        <v>2.555673315764124</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.551498952301571</v>
+        <v>-5.433387135346353</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7535957847772341</v>
+        <v>0.8008405115593207</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6577980000020939</v>
+        <v>-0.626670379754679</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.579872990010353</v>
+        <v>2.598549562158802</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.458498911095672</v>
+        <v>-5.340387094140455</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7719900600433887</v>
+        <v>0.8192347868254757</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6577980000020939</v>
+        <v>-0.626670379754679</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.561067248794149</v>
+        <v>2.579743820942598</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.218068414290812</v>
+        <v>-5.099956597335595</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8699053353902104</v>
+        <v>0.917150062172297</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4173675031972336</v>
+        <v>-0.3862398829498187</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.707068623501943</v>
+        <v>2.725745195650391</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.145825846119617</v>
+        <v>-5.0277140291644</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9027316764935085</v>
+        <v>0.9499764032755951</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4173675031972336</v>
+        <v>-0.3862398829498187</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.710997937336763</v>
+        <v>2.729674509485212</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349963</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.029885996494432</v>
+        <v>-4.911774179539215</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9497862002609225</v>
+        <v>0.9970309270430093</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3405457721811097</v>
+        <v>-0.3094181519336948</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.757769559863777</v>
+        <v>2.776446132012226</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.921081111014705</v>
+        <v>-4.802969294059488</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9903062256728068</v>
+        <v>1.037550952454894</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3405457721811097</v>
+        <v>-0.3094181519336948</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.754767631083771</v>
+        <v>2.77344420323222</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.701060312977694</v>
+        <v>-4.582948496022477</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.079893581898225</v>
+        <v>1.127138308680312</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1993259271131295</v>
+        <v>-0.1681983068657146</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.841078575135173</v>
+        <v>2.859755147283622</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.568192623914417</v>
+        <v>-4.4500808069592</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.14893484032536</v>
+        <v>1.196179567107446</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1993259271131295</v>
+        <v>-0.1681983068657146</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.856972757936996</v>
+        <v>2.875649330085445</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.408677520395047</v>
+        <v>-4.29056570343983</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.213886726173409</v>
+        <v>1.261131452955496</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.03981082359375954</v>
+        <v>-0.008683203346344648</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.95382766448892</v>
+        <v>2.972504236637369</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.26400537529531</v>
+        <v>-4.145893558340092</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.281843686774744</v>
+        <v>1.329088413556831</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1048613215059779</v>
+        <v>0.1359889417533928</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.050719054110202</v>
+        <v>3.069395626258651</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.323880202653002</v>
+        <v>-4.205768385697785</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.243931247233093</v>
+        <v>1.29117597401518</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04498649414828576</v>
+        <v>0.07611411439570065</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.000831649097013</v>
+        <v>3.019508221245462</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.237080704873993</v>
+        <v>-4.118968887918776</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.301051539667263</v>
+        <v>1.34829626644935</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04498649414828576</v>
+        <v>0.07611411439570065</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.023232142419579</v>
+        <v>3.041908714568028</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.239550411335799</v>
+        <v>-4.121438594380582</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.300136058455953</v>
+        <v>1.34738078523804</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.0425167876864796</v>
+        <v>0.07364440793389448</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.021822719915908</v>
+        <v>3.040499292064356</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.307920597659809</v>
+        <v>-4.189808780704592</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.283794906401051</v>
+        <v>1.331039633183137</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.05179248672269454</v>
+        <v>0.08292010697010943</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.038395061812338</v>
+        <v>3.057071633960788</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.186504168033332</v>
+        <v>-4.068392351078115</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.322798186883532</v>
+        <v>1.370042913665619</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.05179248672269454</v>
+        <v>0.08292010697010943</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.02883177044423</v>
+        <v>3.047508342592679</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.217497327362038</v>
+        <v>-4.099385510406821</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.135110488192437</v>
+        <v>1.182355214974524</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.05179248672269454</v>
+        <v>0.08292010697010943</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.853541335484616</v>
+        <v>2.872217907633066</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.042023067569568</v>
+        <v>-3.923911250614351</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.209867424101213</v>
+        <v>1.257112150883299</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.05179248672269454</v>
+        <v>0.08292010697010943</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.858108567476404</v>
+        <v>2.876785139624853</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.152959320210817</v>
+        <v>-4.0348475032556</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.14123495180592</v>
+        <v>1.188479678588007</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.05179248672269454</v>
+        <v>0.08292010697010943</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.833850596237611</v>
+        <v>2.85252716838606</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.35598589775405</v>
+        <v>-4.237874080798833</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.063155706008533</v>
+        <v>1.110400432790619</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1512340908205388</v>
+        <v>-0.120106470573124</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.715166034931577</v>
+        <v>2.733842607080026</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.198060298818757</v>
+        <v>-4.07994848186354</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.136498332014782</v>
+        <v>1.183743058796869</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1512340908205388</v>
+        <v>-0.120106470573124</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.725338421363709</v>
+        <v>2.744014993512158</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.111816835792379</v>
+        <v>-3.993705018837162</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.165941987799193</v>
+        <v>1.21318671458128</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1512340908205388</v>
+        <v>-0.120106470573124</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.720284691937569</v>
+        <v>2.738961264086019</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.112999920443441</v>
+        <v>-3.994888103488223</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.157244529383294</v>
+        <v>1.204489256165381</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1568771392870504</v>
+        <v>-0.1257495190396355</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.708674638302188</v>
+        <v>2.727351210450637</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.989872213449358</v>
+        <v>-3.87176039649414</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.207047485214029</v>
+        <v>1.254292211996116</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1568771392870504</v>
+        <v>-0.1257495190396355</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.70922651133529</v>
+        <v>2.727903083483739</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.897061731998499</v>
+        <v>-3.778949915043281</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.173444369685739</v>
+        <v>1.220689096467826</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06406665783619103</v>
+        <v>-0.03293903758877614</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.694185492097171</v>
+        <v>2.71286206424562</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.848498679777468</v>
+        <v>-3.73038686282225</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.194743066498752</v>
+        <v>1.241987793280839</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.01550360561516084</v>
+        <v>0.01562401463225405</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.72519679935439</v>
+        <v>2.743873371502839</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.735827461541218</v>
+        <v>-3.617715644586</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.234887262304975</v>
+        <v>1.282131989087062</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09716761262108936</v>
+        <v>0.1282952328685042</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.787875238807863</v>
+        <v>2.806551810956312</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.623450460358546</v>
+        <v>-3.505338643403328</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.285329358608711</v>
+        <v>1.332574085390798</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09716761262108936</v>
+        <v>0.1282952328685042</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.79336653463853</v>
+        <v>2.812043106786979</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.821685029245276</v>
+        <v>-3.703573212290058</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.217532732822558</v>
+        <v>1.264777459604645</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1010669562656412</v>
+        <v>-0.06993933601822633</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.685922995075031</v>
+        <v>2.70459956722348</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.904686310270555</v>
+        <v>-3.786574493315337</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.0226879404131</v>
+        <v>1.069932667195187</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.119637840792815</v>
+        <v>-0.08851022054540009</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.51313618435938</v>
+        <v>2.531812756507829</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.745492038213979</v>
+        <v>-3.627380221258761</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.206515309954935</v>
+        <v>1.253760036737023</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.119637840792815</v>
+        <v>-0.08851022054540009</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.633285845078586</v>
+        <v>2.651962417227034</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.832090621195082</v>
+        <v>-3.713978804239864</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.186388902864817</v>
+        <v>1.233633629646905</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.119637840792815</v>
+        <v>-0.08851022054540009</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.647798871180909</v>
+        <v>2.666475443329357</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.793706958636931</v>
+        <v>-3.675595141681713</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.199161809230447</v>
+        <v>1.246406536012534</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.0812541782346638</v>
+        <v>-0.05012655798724891</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.668248510058168</v>
+        <v>2.686925082206617</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.616590628601764</v>
+        <v>-3.498478811646546</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.266737370089815</v>
+        <v>1.313982096871902</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.0812541782346638</v>
+        <v>-0.05012655798724891</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.66497753890347</v>
+        <v>2.683654111051919</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.586888504625471</v>
+        <v>-3.468776687670253</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.279301611442246</v>
+        <v>1.326546338224333</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.08572430344997717</v>
+        <v>-0.05459668320256228</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.662978855536195</v>
+        <v>2.681655427684644</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.407513083386703</v>
+        <v>-3.289401266431485</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.344838755244167</v>
+        <v>1.392083482026254</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.07105245472074151</v>
+        <v>0.1021800749681564</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.750831885745041</v>
+        <v>2.769508457893489</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.452527296907309</v>
+        <v>-3.334415479952091</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.307640525167514</v>
+        <v>1.354885251949602</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.0407035594061369</v>
+        <v>0.07183117965355179</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.713430003887868</v>
+        <v>2.732106576036316</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.719531807179744</v>
+        <v>-3.601419990224526</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.206530283397486</v>
+        <v>1.253775010179573</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1536594786368117</v>
+        <v>-0.1225318583893968</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.602503743401044</v>
+        <v>2.621180315549493</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.00831902763866</v>
+        <v>-3.890207210683442</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.090219317110421</v>
+        <v>1.137464043892508</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.254745598735812</v>
+        <v>-0.2236179784883972</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.541055993238145</v>
+        <v>2.559732565386594</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.056251089267143</v>
+        <v>-3.857731624512669</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.068646454013345</v>
+        <v>1.148054239915134</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.254745598735812</v>
+        <v>-0.2236179784883972</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.538655954792462</v>
+        <v>2.557332526940911</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.709506867848104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.037212961559845</v>
+        <v>-3.838693496805372</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.072786424304509</v>
+        <v>1.152194210206298</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3129292100670066</v>
+        <v>-0.2818015898195917</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.50027050720199</v>
+        <v>2.518947079350439</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.053958826816221</v>
+        <v>-3.855439362061747</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.243669947140639</v>
+        <v>1.323077733042428</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3129292100670066</v>
+        <v>-0.2818015898195917</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.677852376140671</v>
+        <v>2.69652894828912</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.106279207417012</v>
+        <v>-3.907759742662539</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.223575123886456</v>
+        <v>1.302982909788245</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2779823500581344</v>
+        <v>-0.2468547298107195</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.699653821132128</v>
+        <v>2.718330393280576</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.250602113341931</v>
+        <v>-4.052082648587458</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.171854491913414</v>
+        <v>1.251262277815204</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2779823500581344</v>
+        <v>-0.2468547298107195</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.705662351529054</v>
+        <v>2.724338923677502</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.102859143106929</v>
+        <v>-3.904339678352456</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.310104327799437</v>
+        <v>1.389512113701226</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1101749928232513</v>
+        <v>-0.07904737257583638</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.885499413662005</v>
+        <v>2.904175985810455</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651169</v>
+        <v>3.802242353651171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.20487382563815</v>
+        <v>-4.006354360883677</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.27209207631843</v>
+        <v>1.351499862220219</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1101749928232513</v>
+        <v>-0.07904737257583638</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.888293035193486</v>
+        <v>2.906969607341936</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864729</v>
+        <v>3.805605409864731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.068264481544057</v>
+        <v>-3.869745016789584</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.327398162347725</v>
+        <v>1.406805948249514</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02643435127084121</v>
+        <v>0.05756197151825609</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.9709209900416</v>
+        <v>2.989597562190049</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.211029814366707</v>
+        <v>-4.012510349612235</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.269372505958775</v>
+        <v>1.348780291860564</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1163309815518092</v>
+        <v>-0.08520336130439432</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.88434226708812</v>
+        <v>2.903018839236569</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.794318571407198</v>
+        <v>3.848194967147085</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.965788990868945</v>
+        <v>3.054090337734117</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.211029814366707</v>
+        <v>-4.012510349612235</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.269372505958775</v>
+        <v>1.348780291860564</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1163309815518092</v>
+        <v>-0.08520336130439432</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.958852787855313</v>
+        <v>3.047154134720485</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-34.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.9%</t>
+          <t>443.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.8%</t>
+          <t>-602.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-35.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-241.3%</t>
+          <t>-257.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-192.0%</t>
+          <t>-123.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.5%</t>
+          <t>-251.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-141.3%</t>
+          <t>-169.9%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386097</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998565</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082129</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.853637720539343</v>
+        <v>-9.976706868804879</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7999024221113737</v>
+        <v>-0.8491300814175879</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.129372078375717</v>
+        <v>-2.165457029933451</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.864285843392681</v>
+        <v>1.842634872458041</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.780167888871894</v>
+        <v>-10.05654567957966</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7551427879509731</v>
+        <v>-0.8656939042340781</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.055902246708268</v>
+        <v>-2.245295840708228</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.923739443886571</v>
+        <v>1.810103287486595</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.955292306258437</v>
+        <v>-10.2316700969662</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8106373341580735</v>
+        <v>-0.9211884504411785</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.231026664094812</v>
+        <v>-2.420420258094772</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.833220014202162</v>
+        <v>1.719583857802186</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.18974440027293</v>
+        <v>-10.46612219098069</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9116373366654655</v>
+        <v>-1.022188452948571</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.231026664094812</v>
+        <v>-2.420420258094772</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.826000849300566</v>
+        <v>1.71236469290059</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.47754824481017</v>
+        <v>-10.75392603551793</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.033431065254337</v>
+        <v>-1.143982181537442</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.51883050863205</v>
+        <v>-2.70822410263201</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.646646351804247</v>
+        <v>1.533010195404271</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.53033440041049</v>
+        <v>-10.80671219111825</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.053429737655911</v>
+        <v>-1.163980853939016</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.614505995214447</v>
+        <v>-2.803899589214407</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.590356849693365</v>
+        <v>1.476720693293389</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.76236332014675</v>
+        <v>-11.03874111085452</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.143547576921301</v>
+        <v>-1.254098693204406</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.67651869240287</v>
+        <v>-2.86591228640283</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.555842960009426</v>
+        <v>1.44220680360945</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.71034780617794</v>
+        <v>-10.9867255968857</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.118751035647375</v>
+        <v>-1.22930215193048</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.67651869240287</v>
+        <v>-2.86591228640283</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.559833295695827</v>
+        <v>1.446197139295851</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.85201964790206</v>
+        <v>-11.12839743860982</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.176894999235765</v>
+        <v>-1.28744611551887</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.67651869240287</v>
+        <v>-2.86591228640283</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.558358068797085</v>
+        <v>1.444721912397109</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.80242880347723</v>
+        <v>-11.07880659418499</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.142005251300959</v>
+        <v>-1.252556367584064</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.626927847978036</v>
+        <v>-2.816321441977996</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.603165985616857</v>
+        <v>1.489529829216881</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.60327669624013</v>
+        <v>-10.87965448694789</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.075395542052803</v>
+        <v>-1.185946658335908</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.461605322028223</v>
+        <v>-2.650998916028183</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.689308367540062</v>
+        <v>1.575672211140086</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.37743154352072</v>
+        <v>-10.65380933422848</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9754784079288297</v>
+        <v>-1.086029524211935</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.41967864644106</v>
+        <v>-2.609072240441019</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.724043445928569</v>
+        <v>1.610407289528593</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.25285288718313</v>
+        <v>-10.52923067789089</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9245078008377345</v>
+        <v>-1.03505891712084</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.41967864644106</v>
+        <v>-2.609072240441019</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.725182590484628</v>
+        <v>1.611546434084652</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.30574817522741</v>
+        <v>-10.58212596593517</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9430321418933412</v>
+        <v>-1.053583258176446</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.414723300352613</v>
+        <v>-2.604116894352573</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.730789572299803</v>
+        <v>1.617153415899828</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.02183944429866</v>
+        <v>-10.29821723500643</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8237349452832055</v>
+        <v>-0.9342860615663104</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.414723300352613</v>
+        <v>-2.604116894352573</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.73652327653844</v>
+        <v>1.622887120138464</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.950473051689016</v>
+        <v>-10.22685084239678</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8049256506332112</v>
+        <v>-0.9154767669163162</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.343356907742966</v>
+        <v>-2.532750501742925</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.769605849710363</v>
+        <v>1.655969693310388</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.686636184484946</v>
+        <v>-9.963013975192709</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7092743850644911</v>
+        <v>-0.8198255013475961</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.343356907742966</v>
+        <v>-2.532750501742925</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.759722368397456</v>
+        <v>1.64608621199748</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.419394383616549</v>
+        <v>-9.695772174324311</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6042122252165059</v>
+        <v>-0.7147633414996108</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.343356907742966</v>
+        <v>-2.532750501742925</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.757887807898082</v>
+        <v>1.644251651498106</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.321487344940058</v>
+        <v>-9.597865135647821</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5653497247193702</v>
+        <v>-0.6759008410024752</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.275371157882409</v>
+        <v>-2.464764751882369</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.798378942840955</v>
+        <v>1.68474278644098</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.2975338039641</v>
+        <v>-9.573911594671863</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5550998021834936</v>
+        <v>-0.6656509184665986</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.251417616906452</v>
+        <v>-2.440811210906411</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.813419573572023</v>
+        <v>1.699783417172048</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.033473865641303</v>
+        <v>-9.309851656349066</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.462736143016127</v>
+        <v>-0.573287259299232</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.987357678583656</v>
+        <v>-2.176751272583615</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.958595220403949</v>
+        <v>1.844959064003973</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.326394242136466</v>
+        <v>-8.602772032844229</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.182691327274493</v>
+        <v>-0.293242443557598</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.987357678583656</v>
+        <v>-2.176751272583615</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.955808186743648</v>
+        <v>1.842172030343672</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.286209943770276</v>
+        <v>-8.562587734478038</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1662739840401755</v>
+        <v>-0.2768251003232804</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.947173380217465</v>
+        <v>-2.136566974217424</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.980262389651203</v>
+        <v>1.866626233251228</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.206140148232471</v>
+        <v>-8.482517938940234</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1348792446042966</v>
+        <v>-0.2454303608874016</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.867103584679661</v>
+        <v>-2.05649717867962</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.027671088194643</v>
+        <v>1.914034931794667</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.972658926002873</v>
+        <v>-8.249036716710634</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.03356232687460459</v>
+        <v>-0.1441134431577096</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.633622362450062</v>
+        <v>-1.823015956450022</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.175684250370255</v>
+        <v>2.062048093970279</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.822992534995358</v>
+        <v>-8.09937032570312</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.02341201921544211</v>
+        <v>-0.08713909706766287</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.540718871207526</v>
+        <v>-1.730112465207486</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.228534134802817</v>
+        <v>2.114897978402841</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.690717061364471</v>
+        <v>-7.967094852072234</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.07168969541482362</v>
+        <v>-0.03886142086828137</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.40844339757664</v>
+        <v>-1.597836991576599</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.303266905728376</v>
+        <v>2.1896307493284</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.500117386691318</v>
+        <v>-7.776495177399081</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1507446259717216</v>
+        <v>0.04019350968861657</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.217843722903487</v>
+        <v>-1.407237316903446</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.420441771219904</v>
+        <v>2.306805614819929</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.251117588007737</v>
+        <v>-7.5274953787155</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2632508866688128</v>
+        <v>0.1526997703857078</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.217843722903487</v>
+        <v>-1.407237316903446</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.433348112443563</v>
+        <v>2.319711956043587</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.356707577780842</v>
+        <v>-7.633085368488604</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.09303896116035215</v>
+        <v>-0.01751215512275284</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.323433712676591</v>
+        <v>-1.512827306676551</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.242018188980482</v>
+        <v>2.128382032580507</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.375442479899439</v>
+        <v>-7.651820270607201</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1340893421899998</v>
+        <v>0.02353822590689481</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.323433712676591</v>
+        <v>-1.512827306676551</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.290562530857568</v>
+        <v>2.176926374457593</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.22750243849184</v>
+        <v>-7.503880229199602</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07338643606487194</v>
+        <v>-0.03716468021823305</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.303112796768034</v>
+        <v>-1.492506390767993</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.182876157714535</v>
+        <v>2.06924000131456</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.203273802102867</v>
+        <v>-7.47965159281063</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07436390436698259</v>
+        <v>-0.0361872119161224</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.278884160379061</v>
+        <v>-1.468277754379021</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.188699353294441</v>
+        <v>2.075063196894465</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.159725395332177</v>
+        <v>-7.436103186039939</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08482265498016561</v>
+        <v>-0.02572846130293938</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.278884160379061</v>
+        <v>-1.468277754379021</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.181738741199347</v>
+        <v>2.068102584799372</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.917577001878318</v>
+        <v>-7.193954792586081</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.196144366742852</v>
+        <v>0.08559325045974697</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.278884160379061</v>
+        <v>-1.468277754379021</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.19620109558049</v>
+        <v>2.082564939180515</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.85434763010997</v>
+        <v>-7.130725420817733</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2159682359093864</v>
+        <v>0.1054171196262814</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.278884160379061</v>
+        <v>-1.468277754379021</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.190733216039686</v>
+        <v>2.07709705963971</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.731056495292839</v>
+        <v>-7.007434286000602</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2627827838468155</v>
+        <v>0.1522316675637105</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.155593025561931</v>
+        <v>-1.34498661956189</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.262205990940541</v>
+        <v>2.148569834540565</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.709907296389396</v>
+        <v>-6.986285087097158</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2789434416455183</v>
+        <v>0.1683923253624133</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.134443826658488</v>
+        <v>-1.323837420658447</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.282596488519932</v>
+        <v>2.168960332119956</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.466141854405952</v>
+        <v>-6.742519645113714</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3722303267859464</v>
+        <v>0.2616792105028414</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.134443826658488</v>
+        <v>-1.323837420658447</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.278377196866982</v>
+        <v>2.164741040467007</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.319244826688081</v>
+        <v>-6.595622617395843</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.433113451793111</v>
+        <v>0.322562335510006</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.086785584679899</v>
+        <v>-1.276179178679859</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.309096455974151</v>
+        <v>2.195460299574175</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.069394432739006</v>
+        <v>-6.345772223446769</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5257956843564426</v>
+        <v>0.4152445680733376</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.086785584679899</v>
+        <v>-1.276179178679859</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.301838530957853</v>
+        <v>2.188202374557878</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.893502340271574</v>
+        <v>-6.169880130979337</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5997516448640643</v>
+        <v>0.4892005285809593</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.086785584679899</v>
+        <v>-1.276179178679859</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.305437654478502</v>
+        <v>2.191801498078526</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.722055877249111</v>
+        <v>-5.998433667956873</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6816577361276037</v>
+        <v>0.5711066198444987</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9153391216574364</v>
+        <v>-1.104732715657396</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.421633038346534</v>
+        <v>2.307996881946558</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.497022877580288</v>
+        <v>-5.77340066828805</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7706914136114298</v>
+        <v>0.6601402973283248</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.6903061219886135</v>
+        <v>-0.879699715988573</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.555673315764124</v>
+        <v>2.442037159364149</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.433387135346353</v>
+        <v>-5.709764926054116</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8008405115593207</v>
+        <v>0.6902893952762157</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.626670379754679</v>
+        <v>-0.8160639737546385</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.598549562158802</v>
+        <v>2.484913405758827</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.79881119554478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.340387094140455</v>
+        <v>-5.616764884848218</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8192347868254757</v>
+        <v>0.7086836705423707</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.626670379754679</v>
+        <v>-0.8160639737546385</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.579743820942598</v>
+        <v>2.466107664542622</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.099956597335595</v>
+        <v>-5.376334388043357</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.917150062172297</v>
+        <v>0.806598945889192</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3862398829498187</v>
+        <v>-0.5756334769497782</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.725745195650391</v>
+        <v>2.612109039250416</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.0277140291644</v>
+        <v>-5.304091819872163</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9499764032755951</v>
+        <v>0.8394252869924901</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3862398829498187</v>
+        <v>-0.5756334769497782</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.729674509485212</v>
+        <v>2.616038353085236</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.911774179539215</v>
+        <v>-5.188151970246977</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9970309270430093</v>
+        <v>0.8864798107599046</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3094181519336948</v>
+        <v>-0.4988117459336543</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.776446132012226</v>
+        <v>2.66280997561225</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.802969294059488</v>
+        <v>-5.07934708476725</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.037550952454894</v>
+        <v>0.9269998361717886</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3094181519336948</v>
+        <v>-0.4988117459336543</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.77344420323222</v>
+        <v>2.659808046832244</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.582948496022477</v>
+        <v>-4.85932628673024</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.127138308680312</v>
+        <v>1.016587192397207</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1681983068657146</v>
+        <v>-0.3575919008656741</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.859755147283622</v>
+        <v>2.746118990883646</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.4500808069592</v>
+        <v>-4.726458597666962</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.196179567107446</v>
+        <v>1.085628450824341</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1681983068657146</v>
+        <v>-0.3575919008656741</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.875649330085445</v>
+        <v>2.762013173685469</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.29056570343983</v>
+        <v>-4.566943494147592</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.261131452955496</v>
+        <v>1.150580336672391</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.008683203346344648</v>
+        <v>-0.1980767973463041</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.972504236637369</v>
+        <v>2.858868080237393</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.145893558340092</v>
+        <v>-4.422271349047855</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.329088413556831</v>
+        <v>1.218537297273726</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1359889417533928</v>
+        <v>-0.05340465224656671</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.069395626258651</v>
+        <v>2.955759469858676</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.205768385697785</v>
+        <v>-4.482146176405547</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.29117597401518</v>
+        <v>1.180624857732075</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.07611411439570065</v>
+        <v>-0.1132794796042588</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.019508221245462</v>
+        <v>2.905872064845486</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.118968887918776</v>
+        <v>-4.395346678626538</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.34829626644935</v>
+        <v>1.237745150166245</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.07611411439570065</v>
+        <v>-0.1132794796042588</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.041908714568028</v>
+        <v>2.928272558168052</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.121438594380582</v>
+        <v>-4.397816385088344</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.34738078523804</v>
+        <v>1.236829668954935</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.07364440793389448</v>
+        <v>-0.115749186066065</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.040499292064356</v>
+        <v>2.926863135664381</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.189808780704592</v>
+        <v>-4.466186571412354</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.331039633183137</v>
+        <v>1.220488516900032</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.08292010697010943</v>
+        <v>-0.10647348702985</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.057071633960788</v>
+        <v>2.943435477560812</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.068392351078115</v>
+        <v>-4.344770141785878</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.370042913665619</v>
+        <v>1.259491797382514</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.08292010697010943</v>
+        <v>-0.10647348702985</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.047508342592679</v>
+        <v>2.933872186192703</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.099385510406821</v>
+        <v>-4.375763301114583</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.182355214974524</v>
+        <v>1.071804098691419</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.08292010697010943</v>
+        <v>-0.10647348702985</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.872217907633066</v>
+        <v>2.75858175123309</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.923911250614351</v>
+        <v>-4.200289041322113</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.257112150883299</v>
+        <v>1.146561034600195</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.08292010697010943</v>
+        <v>-0.10647348702985</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.876785139624853</v>
+        <v>2.763148983224878</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.0348475032556</v>
+        <v>-4.311225293963362</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.188479678588007</v>
+        <v>1.077928562304902</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.08292010697010943</v>
+        <v>-0.10647348702985</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.85252716838606</v>
+        <v>2.738891011986085</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.237874080798833</v>
+        <v>-4.514251871506596</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.110400432790619</v>
+        <v>0.9998493165075144</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.120106470573124</v>
+        <v>-0.3095000645730834</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.733842607080026</v>
+        <v>2.62020645068005</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.07994848186354</v>
+        <v>-4.356326272571303</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.183743058796869</v>
+        <v>1.073191942513764</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.120106470573124</v>
+        <v>-0.3095000645730834</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.744014993512158</v>
+        <v>2.630378837112183</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.993705018837162</v>
+        <v>-4.270082809544925</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.21318671458128</v>
+        <v>1.102635598298175</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.120106470573124</v>
+        <v>-0.3095000645730834</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.738961264086019</v>
+        <v>2.625325107686043</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.994888103488223</v>
+        <v>-4.271265894195986</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.204489256165381</v>
+        <v>1.093938139882276</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1257495190396355</v>
+        <v>-0.315143113039595</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.727351210450637</v>
+        <v>2.613715054050661</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.87176039649414</v>
+        <v>-4.272512683877278</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.254292211996116</v>
+        <v>1.093991297042861</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1257495190396355</v>
+        <v>-0.315143113039595</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.727903083483739</v>
+        <v>2.614266927083763</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.778949915043281</v>
+        <v>-4.179702202426419</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.220689096467826</v>
+        <v>1.060388181514571</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.03293903758877614</v>
+        <v>-0.2223326315887356</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.71286206424562</v>
+        <v>2.599225907845644</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.73038686282225</v>
+        <v>-4.131139150205389</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.241987793280839</v>
+        <v>1.081686878327583</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.01562401463225405</v>
+        <v>-0.1737695793677054</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.743873371502839</v>
+        <v>2.630237215102863</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.617715644586</v>
+        <v>-4.018467931969139</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.282131989087062</v>
+        <v>1.121831074133806</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1282952328685042</v>
+        <v>-0.06109836113145523</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.806551810956312</v>
+        <v>2.692915654556336</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.505338643403328</v>
+        <v>-3.906090930786466</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.332574085390798</v>
+        <v>1.172273170437543</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1282952328685042</v>
+        <v>-0.06109836113145523</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.812043106786979</v>
+        <v>2.698406950387004</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.703573212290058</v>
+        <v>-4.104325499673196</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.264777459604645</v>
+        <v>1.10447654465139</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.06993933601822633</v>
+        <v>-0.2593329300181858</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.70459956722348</v>
+        <v>2.590963410823504</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.786574493315337</v>
+        <v>-4.187326780698475</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.069932667195187</v>
+        <v>0.9096317522419313</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.08851022054540009</v>
+        <v>-0.2779038145453596</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.531812756507829</v>
+        <v>2.418176600107853</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.627380221258761</v>
+        <v>-4.0281325086419</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.253760036737023</v>
+        <v>1.093459121783767</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.08851022054540009</v>
+        <v>-0.2779038145453596</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.651962417227034</v>
+        <v>2.538326260827059</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.713978804239864</v>
+        <v>-4.114731091623002</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.233633629646905</v>
+        <v>1.073332714693649</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.08851022054540009</v>
+        <v>-0.2779038145453596</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.666475443329357</v>
+        <v>2.552839286929382</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.675595141681713</v>
+        <v>-4.076347429064851</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.246406536012534</v>
+        <v>1.086105621059278</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.05012655798724891</v>
+        <v>-0.2395201519872084</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.686925082206617</v>
+        <v>2.573288925806641</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.498478811646546</v>
+        <v>-3.899231099029685</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.313982096871902</v>
+        <v>1.153681181918647</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.05012655798724891</v>
+        <v>-0.2395201519872084</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.683654111051919</v>
+        <v>2.570017954651943</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.468776687670253</v>
+        <v>-3.869528975053392</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.326546338224333</v>
+        <v>1.166245423271077</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.05459668320256228</v>
+        <v>-0.2439902772025218</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.681655427684644</v>
+        <v>2.568019271284668</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.289401266431485</v>
+        <v>-3.690153553814624</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.392083482026254</v>
+        <v>1.231782567072998</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1021800749681564</v>
+        <v>-0.08721351903180308</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.769508457893489</v>
+        <v>2.655872301493514</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.334415479952091</v>
+        <v>-3.73516776733523</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.354885251949602</v>
+        <v>1.194584336996346</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.07183117965355179</v>
+        <v>-0.1175624143464077</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.732106576036316</v>
+        <v>2.618470419636341</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.601419990224526</v>
+        <v>-4.002172277607666</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.253775010179573</v>
+        <v>1.093474095226317</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1225318583893968</v>
+        <v>-0.3119254523893563</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.621180315549493</v>
+        <v>2.507544159149517</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.890207210683442</v>
+        <v>-4.290959498066581</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.137464043892508</v>
+        <v>0.9771631289392526</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2236179784883972</v>
+        <v>-0.4130115724883566</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.559732565386594</v>
+        <v>2.446096408986619</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.857731624512669</v>
+        <v>-4.258483911895809</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.148054239915134</v>
+        <v>0.9877533249618784</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2236179784883972</v>
+        <v>-0.4130115724883566</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.557332526940911</v>
+        <v>2.443696370540935</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.838693496805372</v>
+        <v>-4.239445784188511</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.152194210206298</v>
+        <v>0.9918932952530422</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2818015898195917</v>
+        <v>-0.4711951838195512</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.518947079350439</v>
+        <v>2.405310922950464</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.855439362061747</v>
+        <v>-4.256191649444887</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.323077733042428</v>
+        <v>1.162776818089173</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2818015898195917</v>
+        <v>-0.4711951838195512</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.69652894828912</v>
+        <v>2.582892791889144</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.907759742662539</v>
+        <v>-4.308512030045678</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.302982909788245</v>
+        <v>1.14268199483499</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2468547298107195</v>
+        <v>-0.436248323810679</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.718330393280576</v>
+        <v>2.604694236880601</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.052082648587458</v>
+        <v>-4.452834935970597</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.251262277815204</v>
+        <v>1.090961362861948</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2468547298107195</v>
+        <v>-0.436248323810679</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.724338923677502</v>
+        <v>2.610702767277527</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.904339678352456</v>
+        <v>-4.305091965735595</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.389512113701226</v>
+        <v>1.229211198747971</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.07904737257583638</v>
+        <v>-0.2684409665757959</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.904175985810455</v>
+        <v>2.790539829410479</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.006354360883677</v>
+        <v>-4.407106648266816</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.351499862220219</v>
+        <v>1.191198947266963</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.07904737257583638</v>
+        <v>-0.2684409665757959</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.906969607341936</v>
+        <v>2.79333345094196</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.869745016789584</v>
+        <v>-4.270497304172723</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.406805948249514</v>
+        <v>1.246505033296259</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.05756197151825609</v>
+        <v>-0.1318316224817034</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.989597562190049</v>
+        <v>2.875961405790073</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360613</v>
+        <v>3.798236219360614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.012510349612235</v>
+        <v>-4.413262636995373</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.348780291860564</v>
+        <v>1.188479376907309</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.08520336130439432</v>
+        <v>-0.2745969553043538</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.903018839236569</v>
+        <v>2.789382682836593</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.848194967147085</v>
+        <v>3.457676512087102</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.054090337734117</v>
+        <v>2.767909508106499</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.012510349612235</v>
+        <v>-4.413262636995373</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.348780291860564</v>
+        <v>1.188479376907309</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.08520336130439432</v>
+        <v>-0.2745969553043538</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.047154134720485</v>
+        <v>2.760973305092867</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-31.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-662.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>443.8%</t>
+          <t>441.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-602.9%</t>
+          <t>-589.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-265.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.3%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-257.4%</t>
+          <t>-252.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.3%</t>
+          <t>-138.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.5%</t>
+          <t>-242.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.9%</t>
+          <t>-166.9%</t>
         </is>
       </c>
     </row>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831155</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355691</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.2518688468972925</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.218881303936446</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.203646580050209</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.203672379819279</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>-0.03348491179958613</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.143760867576903</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>-0.0284473210719996</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.144353344053275</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.1910734010366382</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>3.058049293691157</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.2568407910860502</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>3.032759946801862</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4962344954519427</v>
+        <v>-0.4620854681432948</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.927630497043261</v>
+        <v>2.94129010796672</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5780063958796944</v>
+        <v>-0.5438573685710465</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.885004462827399</v>
+        <v>2.898664073750858</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.6110664764429241</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.876545747435809</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-0.818632260834536</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.791344229798404</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.236386284381373</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.622169511884733</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.473824781011824</v>
+        <v>-1.439675753703176</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.527060329831475</v>
+        <v>2.540719940754934</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9899765505255895</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.681828839364901</v>
+        <v>-1.647679812056253</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448750851044169</v>
+        <v>2.462410461967628</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9899765505255895</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-1.859092232944228</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.372926949950426</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7785641296376145</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.19825061053275</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.230347898221466</v>
       </c>
       <c r="F1851" t="n">
         <v>0.4394057520490924</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.406741391984435</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.167289875379561</v>
       </c>
       <c r="F1852" t="n">
         <v>0.230914970597408</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688091604058305</v>
+        <v>-2.653942576749657</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062848540958581</v>
+        <v>2.076508151882041</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2510683240962204</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180476632082402</v>
+        <v>-3.146327604773754</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.867000921792675</v>
+        <v>1.880660532716134</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2413167039278764</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.531507995703826</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.725130915156968</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-3.875190768930489</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.589426929320919</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3492227559550946</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-4.08170254581751</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.502928277222368</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.555734532842116</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.337543631596203</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.402364769611151</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.76934942474599</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.21597533981864</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-5.004043418878543</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.11038251716771</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.339706066108995</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.9746980499314941</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.703332311009309</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.8357351122056107</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.068459693648055</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.6889386741559433</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.477048470828734</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.5242647072984306</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.753624571144567</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.4088196996435585</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.170016445431564</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.2402570005376368</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.580842483270056</v>
+        <v>-7.546693455961409</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08618527607091897</v>
+        <v>0.09984488699437799</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.926717305254865</v>
+        <v>-7.892568277946218</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05606508757730966</v>
+        <v>-0.04240547665385064</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.090297183439249</v>
+        <v>-8.056148156130602</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1230921187960621</v>
+        <v>-0.1094325078726035</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.386958525249447</v>
+        <v>-8.3528094979408</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2379776795909332</v>
+        <v>-0.2243180686674746</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.510202914464877</v>
+        <v>-8.47605388715623</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2913017398115083</v>
+        <v>-0.2776421288880493</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.893204303207508</v>
+        <v>-8.859055275898861</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4446043966301447</v>
+        <v>-0.4309447857066857</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-9.016454156111982</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.491332821820504</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.375984478615983</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.6297946475240543</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.426333542070205</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.6420182529485658</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.558101846800248</v>
+        <v>-9.523952819491601</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6916838242188144</v>
+        <v>-0.6780242132953553</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.554410921843838</v>
+        <v>-9.52026189453519</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.69020745423625</v>
+        <v>-0.6765478433127909</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.758669097173701</v>
+        <v>-9.724520069865054</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7663975272495529</v>
+        <v>-0.7527379163260943</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.976706868804879</v>
+        <v>-9.942557841496232</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8491300814175879</v>
+        <v>-0.8354704704941294</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.05654567957966</v>
+        <v>-9.869088009828783</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8656939042340781</v>
+        <v>-0.7907108363337283</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.245295840708228</v>
+        <v>-2.091987198266002</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.810103287486595</v>
+        <v>1.902088472951931</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.2316700969662</v>
+        <v>-10.04421242721533</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9211884504411785</v>
+        <v>-0.8462053825408287</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.420420258094772</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.719583857802186</v>
+        <v>1.811569043267521</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.46612219098069</v>
+        <v>-10.27866452122982</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.022188452948571</v>
+        <v>-0.9472053850482207</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.420420258094772</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.71236469290059</v>
+        <v>1.804349878365925</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.75392603551793</v>
+        <v>-10.56646836576705</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.143982181537442</v>
+        <v>-1.068999113637093</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.70822410263201</v>
+        <v>-2.554915460189784</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.533010195404271</v>
+        <v>1.624995380869606</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.80671219111825</v>
+        <v>-10.61925452136738</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.163980853939016</v>
+        <v>-1.088997786038667</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.803899589214407</v>
+        <v>-2.650590946772181</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.476720693293389</v>
+        <v>1.568705878758724</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.03874111085452</v>
+        <v>-10.85128344110364</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.254098693204406</v>
+        <v>-1.179115625304057</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.86591228640283</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.44220680360945</v>
+        <v>1.534191989074785</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.9867255968857</v>
+        <v>-10.79926792713483</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.22930215193048</v>
+        <v>-1.154319084030131</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.86591228640283</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.446197139295851</v>
+        <v>1.538182324761186</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.12839743860982</v>
+        <v>-10.94093976885895</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.28744611551887</v>
+        <v>-1.21246304761852</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.86591228640283</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.444721912397109</v>
+        <v>1.536707097862444</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.07880659418499</v>
+        <v>-10.89134892443412</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.252556367584064</v>
+        <v>-1.177573299683714</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.816321441977996</v>
+        <v>-2.663012799535771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.489529829216881</v>
+        <v>1.581515014682217</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.87965448694789</v>
+        <v>-10.69219681719702</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.185946658335908</v>
+        <v>-1.110963590435558</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.650998916028183</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.575672211140086</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.65380933422848</v>
+        <v>-10.46635166447761</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.086029524211935</v>
+        <v>-1.011046456311586</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.609072240441019</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.610407289528593</v>
+        <v>1.702392474993929</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.52923067789089</v>
+        <v>-10.34177300814001</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.03505891712084</v>
+        <v>-0.9600758492204897</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.609072240441019</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.611546434084652</v>
+        <v>1.703531619549988</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58212596593517</v>
+        <v>-10.3946682961843</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.053583258176446</v>
+        <v>-0.9786001902760963</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.604116894352573</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.617153415899828</v>
+        <v>1.709138601365163</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.29821723500643</v>
+        <v>-10.11075956525555</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9342860615663104</v>
+        <v>-0.8593029936659606</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.604116894352573</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.622887120138464</v>
+        <v>1.7148723056038</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.22685084239678</v>
+        <v>-10.03939317264591</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9154767669163162</v>
+        <v>-0.8404936990159673</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.532750501742925</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.655969693310388</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.963013975192709</v>
+        <v>-9.775556305441835</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8198255013475961</v>
+        <v>-0.7448424334472468</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.532750501742925</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.64608621199748</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.695772174324311</v>
+        <v>-9.508314504573438</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7147633414996108</v>
+        <v>-0.639780273599261</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.532750501742925</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.644251651498106</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.597865135647821</v>
+        <v>-9.410407465896947</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6759008410024752</v>
+        <v>-0.6009177731021258</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.464764751882369</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.68474278644098</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.573911594671863</v>
+        <v>-9.386453924920989</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6656509184665986</v>
+        <v>-0.5906678505662488</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.440811210906411</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.699783417172048</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.309851656349066</v>
+        <v>-9.122393986598192</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.573287259299232</v>
+        <v>-0.4983041913988826</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.176751272583615</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.844959064003973</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.602772032844229</v>
+        <v>-8.415314363093355</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.293242443557598</v>
+        <v>-0.2182593756572482</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.176751272583615</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.842172030343672</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.562587734478038</v>
+        <v>-8.375130064727164</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2768251003232804</v>
+        <v>-0.2018420324229306</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.136566974217424</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.866626233251228</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.482517938940234</v>
+        <v>-8.29506026918936</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2454303608874016</v>
+        <v>-0.1704472929870522</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.05649717867962</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.914034931794667</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.249036716710634</v>
+        <v>-8.061579046959761</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1441134431577096</v>
+        <v>-0.06913037525735977</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.823015956450022</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.062048093970279</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.09937032570312</v>
+        <v>-7.911912655952245</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.08713909706766287</v>
+        <v>-0.01215602916731306</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.730112465207486</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.114897978402841</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.967094852072234</v>
+        <v>-7.779637182321359</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.03886142086828137</v>
+        <v>0.03612164703206844</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.597836991576599</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.1896307493284</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.776495177399081</v>
+        <v>-7.589037507648206</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.04019350968861657</v>
+        <v>0.1151765775889664</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.407237316903446</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.306805614819929</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.5274953787155</v>
+        <v>-7.340037708964625</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1526997703857078</v>
+        <v>0.2276828382860576</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.407237316903446</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.319711956043587</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.633085368488604</v>
+        <v>-7.44562769873773</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.01751215512275284</v>
+        <v>0.05747091277759697</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.512827306676551</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.128382032580507</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.651820270607201</v>
+        <v>-7.464362600856327</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.02353822590689481</v>
+        <v>0.09852129380724461</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.512827306676551</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.176926374457593</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.503880229199602</v>
+        <v>-7.316422559448728</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.03716468021823305</v>
+        <v>0.03781838768211676</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.492506390767993</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.06924000131456</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.47965159281063</v>
+        <v>-7.292193923059755</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0361872119161224</v>
+        <v>0.03879585598422741</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.468277754379021</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.075063196894465</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.436103186039939</v>
+        <v>-7.248645516289065</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02572846130293938</v>
+        <v>0.04925460659741043</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.468277754379021</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.068102584799372</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.193954792586081</v>
+        <v>-7.006497122835206</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08559325045974697</v>
+        <v>0.1605763183600968</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.468277754379021</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.082564939180515</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.130725420817733</v>
+        <v>-6.943267751066858</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1054171196262814</v>
+        <v>0.1804001875266312</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.468277754379021</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.07709705963971</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.007434286000602</v>
+        <v>-6.819976616249727</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1522316675637105</v>
+        <v>0.2272147354640603</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.34498661956189</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.148569834540565</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.986285087097158</v>
+        <v>-6.798827417346284</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1683923253624133</v>
+        <v>0.2433753932627631</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.323837420658447</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.168960332119956</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.742519645113714</v>
+        <v>-6.55506197536284</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2616792105028414</v>
+        <v>0.3366622784031912</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.323837420658447</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.164741040467007</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.595622617395843</v>
+        <v>-6.40816494764497</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.322562335510006</v>
+        <v>0.3975454034103554</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.276179178679859</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.195460299574175</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.345772223446769</v>
+        <v>-6.158314553695895</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4152445680733376</v>
+        <v>0.4902276359736875</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.276179178679859</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.188202374557878</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.169880130979337</v>
+        <v>-5.982422461228463</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4892005285809593</v>
+        <v>0.5641835964813091</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.276179178679859</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.191801498078526</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.998433667956873</v>
+        <v>-5.810975998206</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5711066198444987</v>
+        <v>0.6460896877448481</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.104732715657396</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.307996881946558</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.77340066828805</v>
+        <v>-5.585942998537177</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6601402973283248</v>
+        <v>0.7351233652286742</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.879699715988573</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.442037159364149</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.709764926054116</v>
+        <v>-5.522307256303242</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6902893952762157</v>
+        <v>0.7652724631765651</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8160639737546385</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.484913405758827</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881119554478</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.616764884848218</v>
+        <v>-5.429307215097344</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7086836705423707</v>
+        <v>0.7836667384427201</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8160639737546385</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.466107664542622</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.376334388043357</v>
+        <v>-5.188876718292484</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.806598945889192</v>
+        <v>0.8815820137895418</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5756334769497782</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.612109039250416</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.304091819872163</v>
+        <v>-5.116634150121289</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8394252869924901</v>
+        <v>0.9144083548928399</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5756334769497782</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.616038353085236</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.188151970246977</v>
+        <v>-5.000694300496104</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8864798107599046</v>
+        <v>0.9614628786602539</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4988117459336543</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.66280997561225</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.07934708476725</v>
+        <v>-4.891889415016377</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9269998361717886</v>
+        <v>1.001982904072138</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4988117459336543</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.659808046832244</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.85932628673024</v>
+        <v>-4.671868616979366</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.016587192397207</v>
+        <v>1.091570260297557</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3575919008656741</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.746118990883646</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009948</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.726458597666962</v>
+        <v>-4.539000927916089</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.085628450824341</v>
+        <v>1.160611518724691</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3575919008656741</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.762013173685469</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.566943494147592</v>
+        <v>-4.379485824396719</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.150580336672391</v>
+        <v>1.225563404572741</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1980767973463041</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.858868080237393</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.422271349047855</v>
+        <v>-4.234813679296981</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.218537297273726</v>
+        <v>1.293520365174075</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.05340465224656671</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.955759469858676</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.482146176405547</v>
+        <v>-4.294688506654674</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.180624857732075</v>
+        <v>1.255607925632424</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1132794796042588</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.905872064845486</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.395346678626538</v>
+        <v>-4.207889008875664</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.237745150166245</v>
+        <v>1.312728218066594</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1132794796042588</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.928272558168052</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.397816385088344</v>
+        <v>-4.21035871533747</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.236829668954935</v>
+        <v>1.311812736855284</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.115749186066065</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.926863135664381</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.466186571412354</v>
+        <v>-4.278728901661481</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.220488516900032</v>
+        <v>1.295471584800382</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.10647348702985</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.943435477560812</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.344770141785878</v>
+        <v>-4.157312472035004</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.259491797382514</v>
+        <v>1.334474865282864</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.10647348702985</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.933872186192703</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.375763301114583</v>
+        <v>-4.188305631363709</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.071804098691419</v>
+        <v>1.146787166591768</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.10647348702985</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.75858175123309</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.200289041322113</v>
+        <v>-4.01283137157124</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.146561034600195</v>
+        <v>1.221544102500544</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.10647348702985</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.763148983224878</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.311225293963362</v>
+        <v>-4.123767624212489</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.077928562304902</v>
+        <v>1.152911630205252</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.10647348702985</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.738891011986085</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.514251871506596</v>
+        <v>-4.326794201755722</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9998493165075144</v>
+        <v>1.074832384407864</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3095000645730834</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.62020645068005</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.356326272571303</v>
+        <v>-4.168868602820429</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.073191942513764</v>
+        <v>1.148175010414113</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3095000645730834</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.630378837112183</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.270082809544925</v>
+        <v>-4.082625139794051</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.102635598298175</v>
+        <v>1.177618666198525</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3095000645730834</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.625325107686043</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.271265894195986</v>
+        <v>-4.083808224445113</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.093938139882276</v>
+        <v>1.168921207782626</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.315143113039595</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.613715054050661</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.272512683877278</v>
+        <v>-3.96068051745103</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.093991297042861</v>
+        <v>1.218724163613361</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.315143113039595</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.614266927083763</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.179702202426419</v>
+        <v>-3.984920965454297</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.060388181514571</v>
+        <v>1.138300676303419</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2223326315887356</v>
+        <v>-0.1860749186006367</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.599225907845644</v>
+        <v>2.620980535638504</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.131139150205389</v>
+        <v>-3.936357913233267</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.081686878327583</v>
+        <v>1.159599373116432</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1737695793677054</v>
+        <v>-0.1375118663796066</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.630237215102863</v>
+        <v>2.651991842895722</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.018467931969139</v>
+        <v>-3.823686694997017</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.121831074133806</v>
+        <v>1.199743568922655</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.06109836113145523</v>
+        <v>-0.02484064814335635</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.692915654556336</v>
+        <v>2.714670282349195</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.906090930786466</v>
+        <v>-3.711309693814344</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.172273170437543</v>
+        <v>1.250185665226391</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.06109836113145523</v>
+        <v>-0.02484064814335635</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.698406950387004</v>
+        <v>2.720161578179863</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.104325499673196</v>
+        <v>-3.909544262701075</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.10447654465139</v>
+        <v>1.182389039440238</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2593329300181858</v>
+        <v>-0.2230752170300869</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.590963410823504</v>
+        <v>2.612718038616364</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.187326780698475</v>
+        <v>-3.992545543726354</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9096317522419313</v>
+        <v>0.98754424703078</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2779038145453596</v>
+        <v>-0.2416461015572607</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.418176600107853</v>
+        <v>2.439931227900713</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.0281325086419</v>
+        <v>-3.833351271669777</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.093459121783767</v>
+        <v>1.171371616572616</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2779038145453596</v>
+        <v>-0.2416461015572607</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.538326260827059</v>
+        <v>2.560080888619918</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660769</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.114731091623002</v>
+        <v>-3.91994985465088</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.073332714693649</v>
+        <v>1.151245209482498</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2779038145453596</v>
+        <v>-0.2416461015572607</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.552839286929382</v>
+        <v>2.574593914722241</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383424</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.076347429064851</v>
+        <v>-3.881566192092729</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.086105621059278</v>
+        <v>1.164018115848127</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2395201519872084</v>
+        <v>-0.2032624389991095</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.573288925806641</v>
+        <v>2.5950435535995</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002485</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.899231099029685</v>
+        <v>-3.704449862057563</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.153681181918647</v>
+        <v>1.231593676707496</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2395201519872084</v>
+        <v>-0.2032624389991095</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.570017954651943</v>
+        <v>2.591772582444802</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263903</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.869528975053392</v>
+        <v>-3.674747738081269</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.166245423271077</v>
+        <v>1.244157918059926</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2439902772025218</v>
+        <v>-0.2077325642144229</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.568019271284668</v>
+        <v>2.589773899077528</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.690153553814624</v>
+        <v>-3.495372316842501</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.231782567072998</v>
+        <v>1.309695061861848</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.08721351903180308</v>
+        <v>-0.0509558060437042</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.655872301493514</v>
+        <v>2.677626929286373</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.73516776733523</v>
+        <v>-3.540386530363107</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.194584336996346</v>
+        <v>1.272496831785195</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1175624143464077</v>
+        <v>-0.08130470135830881</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.618470419636341</v>
+        <v>2.6402250474292</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.002172277607666</v>
+        <v>-3.807391040635543</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.093474095226317</v>
+        <v>1.171386590015167</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3119254523893563</v>
+        <v>-0.2756677394012574</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.507544159149517</v>
+        <v>2.529298786942377</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.290959498066581</v>
+        <v>-4.096178261094458</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9771631289392526</v>
+        <v>1.055075623728102</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4130115724883566</v>
+        <v>-0.3767538595002577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.446096408986619</v>
+        <v>2.467851036779478</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285456</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.258483911895809</v>
+        <v>-4.063702674923686</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9877533249618784</v>
+        <v>1.065665819750727</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4130115724883566</v>
+        <v>-0.3767538595002577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.443696370540935</v>
+        <v>2.465450998333795</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848104</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.239445784188511</v>
+        <v>-4.106139092988057</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9918932952530422</v>
+        <v>1.045215971733224</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4711951838195512</v>
+        <v>-0.381854917053519</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.405310922950464</v>
+        <v>2.458915083010083</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.256191649444887</v>
+        <v>-4.122884958244432</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.162776818089173</v>
+        <v>1.216099494569354</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4711951838195512</v>
+        <v>-0.381854917053519</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.582892791889144</v>
+        <v>2.636496951948764</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.308512030045678</v>
+        <v>-4.175205338845224</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.14268199483499</v>
+        <v>1.196004671315171</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.436248323810679</v>
+        <v>-0.3469080570446469</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.604694236880601</v>
+        <v>2.65829839694022</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.452834935970597</v>
+        <v>-4.319528244770143</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.090961362861948</v>
+        <v>1.14428403934213</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.436248323810679</v>
+        <v>-0.3469080570446469</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.610702767277527</v>
+        <v>2.664306927337146</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.305091965735595</v>
+        <v>-4.17178527453514</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.229211198747971</v>
+        <v>1.282533875228153</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2684409665757959</v>
+        <v>-0.1791006998097637</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.790539829410479</v>
+        <v>2.844143989470098</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651171</v>
+        <v>3.802242353651169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.407106648266816</v>
+        <v>-4.273799957066362</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.191198947266963</v>
+        <v>1.244521623747145</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2684409665757959</v>
+        <v>-0.1791006998097637</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.79333345094196</v>
+        <v>2.846937611001579</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864731</v>
+        <v>3.805605409864729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.270497304172723</v>
+        <v>-4.137190612972269</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.246505033296259</v>
+        <v>1.29982770977644</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1318316224817034</v>
+        <v>-0.04249135571567125</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.875961405790073</v>
+        <v>2.929565565849693</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360614</v>
+        <v>3.583611430391693</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.413262636995373</v>
+        <v>-4.279955945794919</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.188479376907309</v>
+        <v>1.241802053387491</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2745969553043538</v>
+        <v>-0.1852566885383217</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.789382682836593</v>
+        <v>2.842986842896213</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.457676512087102</v>
+        <v>3.482044269097198</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.767909508106499</v>
+        <v>2.798047429954387</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.413262636995373</v>
+        <v>-4.279955945794919</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.188479376907309</v>
+        <v>1.241802053387491</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2745969553043538</v>
+        <v>-0.1852566885383217</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.760973305092867</v>
+        <v>2.791111226940755</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-662.0%</t>
+          <t>-677.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.7%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-589.6%</t>
+          <t>-588.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-265.2%</t>
+          <t>-271.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-108.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-252.0%</t>
+          <t>-260.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-304.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-138.9%</t>
+          <t>-146.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-242.5%</t>
+          <t>-260.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-183.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-180.6%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2518688468972925</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.218881303936446</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.203646580050209</v>
+        <v>0.04790760397142968</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.203672379819279</v>
+        <v>3.141376789387767</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.657162997990651</v>
+        <v>1.53557304922052</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.116867970907334</v>
+        <v>4.043914001645255</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.03348491179958613</v>
+        <v>-0.1892238878783654</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.143760867576903</v>
+        <v>3.081465277145391</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.657162997990651</v>
+        <v>1.53557304922052</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.151809055404875</v>
+        <v>4.078855086142797</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.0284473210719996</v>
+        <v>-0.1841862971507789</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.144353344053275</v>
+        <v>3.082057753621763</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.712807454256969</v>
+        <v>1.591217505486837</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.110819200087925</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1910734010366382</v>
+        <v>-0.3468123771154175</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.058049293691157</v>
+        <v>2.995753703259645</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.55018137429233</v>
+        <v>1.428591425522199</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.064943902994957</v>
+        <v>3.991989933732879</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2568407910860502</v>
+        <v>-0.4125797671648295</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.032759946801862</v>
+        <v>2.970464356370351</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.55018137429233</v>
+        <v>1.428591425522199</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.065961512125428</v>
+        <v>3.993007542863349</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4620854681432948</v>
+        <v>-0.6178244442220742</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.94129010796672</v>
+        <v>2.878994517535209</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.55018137429233</v>
+        <v>1.428591425522199</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.056589544113184</v>
+        <v>3.983635574851105</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5438573685710465</v>
+        <v>-0.6995963446498259</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.898664073750858</v>
+        <v>2.836368483319346</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.577216947698467</v>
+        <v>1.455626998928335</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.062893614112104</v>
+        <v>3.989939644850025</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6110664764429241</v>
+        <v>-0.7668054525217036</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.876545747435809</v>
+        <v>2.814250157004297</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.577216947698467</v>
+        <v>1.455626998928335</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.067658930945806</v>
+        <v>3.994704961683727</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.818632260834536</v>
+        <v>-0.9743712369133155</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.791344229798404</v>
+        <v>2.729048639366892</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.369651163306855</v>
+        <v>1.248061214536723</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940944256430079</v>
+        <v>3.867990287168</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.236386284381373</v>
+        <v>-1.392125260460152</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.622169511884733</v>
+        <v>2.559873921453221</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9518971397600179</v>
+        <v>0.8303071909898864</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.68821873380704</v>
+        <v>3.615264764544961</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.439675753703176</v>
+        <v>-1.595414729781955</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.540719940754934</v>
+        <v>2.478424350323422</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9899765505255895</v>
+        <v>0.8683866017554581</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.710932596865305</v>
+        <v>3.637978627603226</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.647679812056253</v>
+        <v>-1.803418788135032</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.462410461967628</v>
+        <v>2.400114871536116</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9899765505255895</v>
+        <v>0.8683866017554581</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.71582474141923</v>
+        <v>3.642870772157151</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.859092232944228</v>
+        <v>-2.014831209023008</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.372926949950426</v>
+        <v>2.310631359518914</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7785641296376145</v>
+        <v>0.656974180867483</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.584058745224433</v>
+        <v>3.511104775962355</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.19825061053275</v>
+        <v>-2.35398958661153</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.230347898221466</v>
+        <v>2.168052307789954</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4394057520490924</v>
+        <v>0.317815803278961</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.373648017977769</v>
+        <v>3.300694048715691</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.406741391984435</v>
+        <v>-2.562480368063214</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.167289875379561</v>
+        <v>2.104994284948049</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.230914970597408</v>
+        <v>0.1093250218272765</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.268891838845527</v>
+        <v>3.195937869583448</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.653942576749657</v>
+        <v>-2.809681552828436</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.076508151882041</v>
+        <v>2.014212561450529</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2510683240962204</v>
+        <v>0.129478375326089</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.289082601353383</v>
+        <v>3.216128632091304</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.146327604773754</v>
+        <v>-3.302066580852533</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.880660532716134</v>
+        <v>1.818364942284622</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.3629066526980078</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.994757976582657</v>
+        <v>2.921804007320578</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.531507995703826</v>
+        <v>-3.687246971782605</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.725130915156968</v>
+        <v>1.662835324725457</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.3629066526980078</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.993300515395521</v>
+        <v>2.920346546133441</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.875190768930489</v>
+        <v>-4.030929745009268</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.589426929320919</v>
+        <v>1.527131338889408</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3492227559550946</v>
+        <v>-0.470812704725226</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.930326007633806</v>
+        <v>2.857372038371727</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.08170254581751</v>
+        <v>-4.237441521896289</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.502928277222368</v>
+        <v>1.440632686790857</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.6773244816122475</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.802525000157851</v>
+        <v>2.729571030895772</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.337543631596203</v>
+        <v>-4.493282607674982</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.402364769611151</v>
+        <v>1.340069179179639</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.6773244816122475</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.80429792685811</v>
+        <v>2.731343957596031</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.76934942474599</v>
+        <v>-4.92508840082477</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.21597533981864</v>
+        <v>1.153679749387129</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.692152029283383</v>
+        <v>-0.8137419780535144</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.708780316460754</v>
+        <v>2.635826347198675</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.004043418878543</v>
+        <v>-5.159782394957322</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.11038251716771</v>
+        <v>1.048086926736199</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.8074057108242593</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.700866851800398</v>
+        <v>2.627912882538319</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.339706066108995</v>
+        <v>-5.495445042187774</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9746980499314941</v>
+        <v>0.9124024594999827</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.8074057108242593</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.699447443456363</v>
+        <v>2.626493474194284</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.703332311009309</v>
+        <v>-5.859071287088088</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8357351122056107</v>
+        <v>0.7734395217740988</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7840373989212537</v>
+        <v>-0.9056273476913851</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.647002021570329</v>
+        <v>2.574048052308251</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.068459693648055</v>
+        <v>-6.224198669726834</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6889386741559433</v>
+        <v>0.6266430837244314</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-1.201938131990398</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.395516096734674</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.477048470828734</v>
+        <v>-6.632787446907512</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5242647072984306</v>
+        <v>0.4619691168669195</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.610526909171076</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.149124374441026</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.753624571144567</v>
+        <v>-6.909363547223345</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4088196996435585</v>
+        <v>0.346524109212047</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.610526909171076</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.144309806912487</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.170016445431564</v>
+        <v>-7.325755421510342</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2402570005376368</v>
+        <v>0.1779614101061253</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.610526909171076</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.142303857521364</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.546693455961409</v>
+        <v>-7.702432432040187</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.09984488699437799</v>
+        <v>0.03754929656286654</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.610526909171076</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.152562548190043</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.892568277946218</v>
+        <v>-8.048307254024996</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.04240547665385064</v>
+        <v>-0.1047010670853621</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.610526909171076</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.148662113335738</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.056148156130602</v>
+        <v>-8.21188713220938</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1094325078726035</v>
+        <v>-0.1717280983041145</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.610526909171076</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.147067033390739</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.3528094979408</v>
+        <v>-8.508548474019578</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2243180686674746</v>
+        <v>-0.2866136590989856</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.679270044904955</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.10960012787962</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.47605388715623</v>
+        <v>-8.631792863235008</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2776421288880493</v>
+        <v>-0.3399377193195607</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.679270044904955</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.105573823345217</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.859055275898861</v>
+        <v>-9.014794251977639</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4309447857066857</v>
+        <v>-0.4932403761381972</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.679270044904955</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.105471722023633</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.016454156111982</v>
+        <v>-9.17219313219076</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.491332821820504</v>
+        <v>-0.5536284122520154</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.836668925118076</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.013603909867191</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.375984478615983</v>
+        <v>-9.531723454694761</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6297946475240543</v>
+        <v>-0.6920902379555658</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.836668925118076</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.018954213165241</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.426333542070205</v>
+        <v>-9.582072518148983</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6420182529485658</v>
+        <v>-0.7043138433800773</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.887017988572298</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>1.996660795049885</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.523952819491601</v>
+        <v>-9.679691795570379</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6780242132953553</v>
+        <v>-0.7403198037268668</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.984637265993695</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.014084948480895</v>
+        <v>1.941130979218816</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.52026189453519</v>
+        <v>-9.676000870613969</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6765478433127909</v>
+        <v>-0.7388434337443024</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.984637265993695</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.014084948480895</v>
+        <v>1.941130979218816</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.724520069865054</v>
+        <v>-9.880259045943832</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7527379163260943</v>
+        <v>-0.8150335067576053</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.990686261837552</v>
+        <v>-2.112276210607683</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.943014778831144</v>
+        <v>1.870060809569065</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.942557841496232</v>
+        <v>-10.09829681757501</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8354704704941294</v>
+        <v>-0.8977660609256408</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.165457029933451</v>
+        <v>-2.287046978703582</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.842634872458041</v>
+        <v>1.769680903195962</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.869088009828783</v>
+        <v>-10.02482698590756</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7907108363337283</v>
+        <v>-0.8530064267652397</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.091987198266002</v>
+        <v>-2.213577147036134</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.902088472951931</v>
+        <v>1.829134503689852</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.04421242721533</v>
+        <v>-10.1999514032941</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8462053825408287</v>
+        <v>-0.9085009729723401</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.388701564422678</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.811569043267521</v>
+        <v>1.738615074005442</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.27866452122982</v>
+        <v>-10.43440349730859</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9472053850482207</v>
+        <v>-1.009500975479732</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.388701564422678</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.804349878365925</v>
+        <v>1.731395909103846</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.56646836576705</v>
+        <v>-10.72220734184583</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.068999113637093</v>
+        <v>-1.131294704068603</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.554915460189784</v>
+        <v>-2.676505408959916</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.624995380869606</v>
+        <v>1.552041411607527</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.61925452136738</v>
+        <v>-10.77499349744616</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.088997786038667</v>
+        <v>-1.151293376470178</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.650590946772181</v>
+        <v>-2.772180895542313</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.568705878758724</v>
+        <v>1.495751909496646</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.85128344110364</v>
+        <v>-11.00702241718242</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.179115625304057</v>
+        <v>-1.241411215735568</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.834193592730736</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.534191989074785</v>
+        <v>1.461238019812706</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.79926792713483</v>
+        <v>-10.95500690321361</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.154319084030131</v>
+        <v>-1.216614674461642</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.834193592730736</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.538182324761186</v>
+        <v>1.465228355499107</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.94093976885895</v>
+        <v>-11.09667874493773</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.21246304761852</v>
+        <v>-1.274758638050032</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.834193592730736</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.536707097862444</v>
+        <v>1.463753128600365</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.89134892443412</v>
+        <v>-11.04708790051289</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.177573299683714</v>
+        <v>-1.239868890115226</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.663012799535771</v>
+        <v>-2.784602748305902</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.581515014682217</v>
+        <v>1.508561045420138</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.69219681719702</v>
+        <v>-10.84793579327579</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.110963590435558</v>
+        <v>-1.173259180867069</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.619280222356089</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.594703427343343</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.46635166447761</v>
+        <v>-10.62209064055638</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.011046456311586</v>
+        <v>-1.073342046743096</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.577353546768925</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.62943850573185</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.34177300814001</v>
+        <v>-10.49751198421879</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9600758492204897</v>
+        <v>-1.022371439652</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.577353546768925</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.630577650287909</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.3946682961843</v>
+        <v>-10.55040727226308</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9786001902760963</v>
+        <v>-1.040895780707607</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.572398200680479</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.636184632103084</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.11075956525555</v>
+        <v>-10.26649854133433</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8593029936659606</v>
+        <v>-0.9215985840974712</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.572398200680479</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.64191833634172</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.03939317264591</v>
+        <v>-10.19513214872468</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8404936990159673</v>
+        <v>-0.9027892894474778</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.501031808070831</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.675000909513644</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.775556305441835</v>
+        <v>-9.931295281520612</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7448424334472468</v>
+        <v>-0.8071380238787573</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.501031808070831</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.665117428200736</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.508314504573438</v>
+        <v>-9.664053480652214</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.639780273599261</v>
+        <v>-0.7020758640307716</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.501031808070831</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.663282867701363</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781948</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.410407465896947</v>
+        <v>-9.566146441975723</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6009177731021258</v>
+        <v>-0.6632133635336364</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.433046058210275</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.703774002644236</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.386453924920989</v>
+        <v>-9.542192900999765</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5906678505662488</v>
+        <v>-0.6529634409977594</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.409092517234317</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.718814633375304</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.122393986598192</v>
+        <v>-9.278132962676969</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4983041913988826</v>
+        <v>-0.5605997818303932</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.145032578911521</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.863990280207229</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.415314363093355</v>
+        <v>-8.571053339172131</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2182593756572482</v>
+        <v>-0.2805549660887587</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.145032578911521</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.861203246546928</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.375130064727164</v>
+        <v>-8.530869040805941</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2018420324229306</v>
+        <v>-0.2641376228544412</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-2.104848280545331</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.885657449454484</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.29506026918936</v>
+        <v>-8.450799245268136</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1704472929870522</v>
+        <v>-0.2327428834185628</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-2.024778485007527</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>1.933066147997923</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.061579046959761</v>
+        <v>-8.217318023038537</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.06913037525735977</v>
+        <v>-0.1314259656888703</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.791297262777928</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.081079310173535</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.911912655952245</v>
+        <v>-8.067651632031023</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.01215602916731306</v>
+        <v>-0.07445161959882407</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.698393771535392</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.133929194606098</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.779637182321359</v>
+        <v>-7.935376158400136</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.03612164703206844</v>
+        <v>-0.02617394339944257</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.566118297904505</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.208661965531657</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.589037507648206</v>
+        <v>-7.862793171524056</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1151765775889664</v>
+        <v>0.00567431203862645</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.493535311028426</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.255026818344941</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.340037708964625</v>
+        <v>-7.613793372840475</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2276828382860576</v>
+        <v>0.1181805727357177</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.493535311028426</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.2679331595686</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.44562769873773</v>
+        <v>-7.71938336261358</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.05747091277759697</v>
+        <v>-0.05203135277274296</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.59912530080153</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.076603236105519</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.464362600856327</v>
+        <v>-7.738118264732177</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.09852129380724461</v>
+        <v>-0.01098097174309531</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.59912530080153</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.125147577982605</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.316422559448728</v>
+        <v>-7.590178223324577</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.03781838768211676</v>
+        <v>-0.07168387786822317</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.578804384892972</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.017461204839572</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.292193923059755</v>
+        <v>-7.565949586935605</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.03879585598422741</v>
+        <v>-0.07070640956611252</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.554575748504</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.023284400419477</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.248645516289065</v>
+        <v>-7.522401180164914</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.04925460659741043</v>
+        <v>-0.06024765895292949</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.554575748504</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.016323788324384</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.006497122835206</v>
+        <v>-7.280252786711056</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1605763183600968</v>
+        <v>0.05107405280975685</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.554575748504</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.030786142705527</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.943267751066858</v>
+        <v>-7.217023414942708</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1804001875266312</v>
+        <v>0.0708979219762913</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.554575748504</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.025318263164722</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262046</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.819976616249727</v>
+        <v>-7.093732280125577</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2272147354640603</v>
+        <v>0.1177124699137204</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.43128461368687</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.096791038065577</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.798827417346284</v>
+        <v>-7.072583081222134</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2433753932627631</v>
+        <v>0.1338731277124232</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.410135414783426</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.117181535644968</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.55506197536284</v>
+        <v>-6.828817639238689</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3366622784031912</v>
+        <v>0.2271600128528513</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.410135414783426</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.112962243992019</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.40816494764497</v>
+        <v>-6.68192061152082</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3975454034103554</v>
+        <v>0.2880431378600155</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.362477172804838</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.143681503099188</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.158314553695895</v>
+        <v>-6.432070217571745</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4902276359736875</v>
+        <v>0.3807253704233475</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.362477172804838</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.13642357808289</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.982422461228463</v>
+        <v>-6.256178125104313</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5641835964813091</v>
+        <v>0.4546813309309687</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.362477172804838</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.140022701603539</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.810975998206</v>
+        <v>-6.084731662081849</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6460896877448481</v>
+        <v>0.5365874221945082</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-1.191030709782375</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.25621808547157</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.585942998537177</v>
+        <v>-5.859698662413027</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7351233652286742</v>
+        <v>0.6256210996783342</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.9659977101135523</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.390258362889161</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.522307256303242</v>
+        <v>-5.796062920179092</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7652724631765651</v>
+        <v>0.6557701976262251</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.9023619678796178</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.433134609283839</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.429307215097344</v>
+        <v>-5.703062878973194</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7836667384427201</v>
+        <v>0.6741644728923801</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.9023619678796178</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.414328868067635</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.188876718292484</v>
+        <v>-5.462632382168334</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8815820137895418</v>
+        <v>0.7720797482392019</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.6619314710747575</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.560330242775428</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.116634150121289</v>
+        <v>-5.390389813997139</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9144083548928399</v>
+        <v>0.8049060893425</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.6619314710747575</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.564259556610248</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.000694300496104</v>
+        <v>-5.274449964371954</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9614628786602539</v>
+        <v>0.851960613109914</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.5851097400586336</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.611031179137263</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.891889415016377</v>
+        <v>-5.165645078892227</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.001982904072138</v>
+        <v>0.892480638521798</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.5851097400586336</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.608029250357256</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.671868616979366</v>
+        <v>-4.945624280855216</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.091570260297557</v>
+        <v>0.9820679947472166</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.4438898949906533</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.694340194408658</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.539000927916089</v>
+        <v>-4.812756591791938</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.160611518724691</v>
+        <v>1.051109253174351</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.4438898949906533</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.710234377210482</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.379485824396719</v>
+        <v>-4.653241488272569</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.225563404572741</v>
+        <v>1.116061139022401</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>-0.2843747914712834</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.807089283762406</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.234813679296981</v>
+        <v>-4.508569343172831</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.293520365174075</v>
+        <v>1.184018099623735</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>-0.139702646371546</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>2.903980673383688</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.294688506654674</v>
+        <v>-4.568444170530523</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.255607925632424</v>
+        <v>1.146105660082084</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.1995774737292381</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>2.854093268370498</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.207889008875664</v>
+        <v>-4.481644672751514</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.312728218066594</v>
+        <v>1.203225952516254</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.1995774737292381</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>2.876493761693065</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.21035871533747</v>
+        <v>-4.48411437921332</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.311812736855284</v>
+        <v>1.202310471304944</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>-0.2020471801910443</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>2.875084339189393</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.278728901661481</v>
+        <v>-4.55248456553733</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.295471584800382</v>
+        <v>1.185969319250042</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1927714811548293</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>2.891656681085824</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.157312472035004</v>
+        <v>-4.431068135910854</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.334474865282864</v>
+        <v>1.224972599732524</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1927714811548293</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>2.882093389717715</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.188305631363709</v>
+        <v>-4.462061295239559</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.146787166591768</v>
+        <v>1.037284901041428</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1927714811548293</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.706802954758102</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.01283137157124</v>
+        <v>-4.28658703544709</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.221544102500544</v>
+        <v>1.112041836950204</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1927714811548293</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.71137018674989</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.123767624212489</v>
+        <v>-4.397523288088339</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.152911630205252</v>
+        <v>1.043409364654912</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1927714811548293</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.687112215511097</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.326794201755722</v>
+        <v>-4.600549865631572</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.074832384407864</v>
+        <v>0.9653301188575238</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.3957980586980627</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.568427654205062</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.168868602820429</v>
+        <v>-4.442624266696279</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.148175010414113</v>
+        <v>1.038672744863773</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.3957980586980627</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.578600040637195</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.082625139794051</v>
+        <v>-4.356380803669901</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.177618666198525</v>
+        <v>1.068116400648185</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.3957980586980627</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.573546311211055</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.083808224445113</v>
+        <v>-4.357563888320962</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.168921207782626</v>
+        <v>1.059418942232286</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.4014411071645743</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.561936257575674</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273188</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.96068051745103</v>
+        <v>-4.234436181326879</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.218724163613361</v>
+        <v>1.109221898063021</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.4014411071645743</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.562488130608775</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279497</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.984920965454297</v>
+        <v>-4.14162569987602</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.138300676303419</v>
+        <v>1.07561878253473</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1860749186006367</v>
+        <v>-0.3086306257137149</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.620980535638504</v>
+        <v>2.547447111370657</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030425</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.936357913233267</v>
+        <v>-4.09306264765499</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.159599373116432</v>
+        <v>1.096917479347743</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1375118663796066</v>
+        <v>-0.2600675734926847</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.651991842895722</v>
+        <v>2.578458418627875</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942737</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.823686694997017</v>
+        <v>-3.98039142941874</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.199743568922655</v>
+        <v>1.137061675153966</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02484064814335635</v>
+        <v>-0.1473963552564345</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.714670282349195</v>
+        <v>2.641136858081349</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.711309693814344</v>
+        <v>-3.868014428236067</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.250185665226391</v>
+        <v>1.187503771457702</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02484064814335635</v>
+        <v>-0.1473963552564345</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.720161578179863</v>
+        <v>2.646628153912016</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.909544262701075</v>
+        <v>-4.066248997122798</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.182389039440238</v>
+        <v>1.119707145671549</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2230752170300869</v>
+        <v>-0.3456309241431651</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.612718038616364</v>
+        <v>2.539184614348517</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.992545543726354</v>
+        <v>-4.149250278148076</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.98754424703078</v>
+        <v>0.9248623532620908</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2416461015572607</v>
+        <v>-0.3642018086703389</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.439931227900713</v>
+        <v>2.366397803632866</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.833351271669777</v>
+        <v>-3.9900560060915</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.171371616572616</v>
+        <v>1.108689722803927</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2416461015572607</v>
+        <v>-0.3642018086703389</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.560080888619918</v>
+        <v>2.486547464352071</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.91994985465088</v>
+        <v>-4.076654589072604</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.151245209482498</v>
+        <v>1.088563315713809</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2416461015572607</v>
+        <v>-0.3642018086703389</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.574593914722241</v>
+        <v>2.501060490454394</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.881566192092729</v>
+        <v>-4.038270926514453</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.164018115848127</v>
+        <v>1.101336222079438</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2032624389991095</v>
+        <v>-0.3258181461121877</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.5950435535995</v>
+        <v>2.521510129331654</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.704449862057563</v>
+        <v>-3.861154596479286</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.231593676707496</v>
+        <v>1.168911782938806</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2032624389991095</v>
+        <v>-0.3258181461121877</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.591772582444802</v>
+        <v>2.518239158176955</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.674747738081269</v>
+        <v>-3.831452472502993</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.244157918059926</v>
+        <v>1.181476024291237</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2077325642144229</v>
+        <v>-0.330288271327501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.589773899077528</v>
+        <v>2.516240474809681</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.495372316842501</v>
+        <v>-3.652077051264225</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.309695061861848</v>
+        <v>1.247013168093158</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.0509558060437042</v>
+        <v>-0.1735115131567824</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.677626929286373</v>
+        <v>2.604093505018526</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.540386530363107</v>
+        <v>-3.697091264784831</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.272496831785195</v>
+        <v>1.209814938016505</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08130470135830881</v>
+        <v>-0.203860408471387</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.6402250474292</v>
+        <v>2.566691623161353</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.807391040635543</v>
+        <v>-3.964095775057267</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.171386590015167</v>
+        <v>1.108704696246477</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2756677394012574</v>
+        <v>-0.3982234465143356</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.529298786942377</v>
+        <v>2.45576536267453</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.096178261094458</v>
+        <v>-4.252882995516182</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.055075623728102</v>
+        <v>0.9923937299594123</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3767538595002577</v>
+        <v>-0.4993095666133359</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.467851036779478</v>
+        <v>2.394317612511631</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.063702674923686</v>
+        <v>-4.22040740934541</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.065665819750727</v>
+        <v>1.002983925982038</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3767538595002577</v>
+        <v>-0.4993095666133359</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.465450998333795</v>
+        <v>2.391917574065948</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.106139092988057</v>
+        <v>-4.201369281638113</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.045215971733224</v>
+        <v>1.007123896273202</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.381854917053519</v>
+        <v>-0.5574931779445305</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.458915083010083</v>
+        <v>2.353532126475476</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.122884958244432</v>
+        <v>-4.218115146894488</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.216099494569354</v>
+        <v>1.178007419109332</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.381854917053519</v>
+        <v>-0.5574931779445305</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.636496951948764</v>
+        <v>2.531113995414156</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537864</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.175205338845224</v>
+        <v>-4.270435527495279</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.196004671315171</v>
+        <v>1.157912595855149</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3469080570446469</v>
+        <v>-0.5225463179356583</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.65829839694022</v>
+        <v>2.552915440405613</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.319528244770143</v>
+        <v>-4.414758433420198</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.14428403934213</v>
+        <v>1.106191963882107</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3469080570446469</v>
+        <v>-0.5225463179356583</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.664306927337146</v>
+        <v>2.558923970802539</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.17178527453514</v>
+        <v>-4.267015463185196</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.282533875228153</v>
+        <v>1.24444179976813</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1791006998097637</v>
+        <v>-0.3547389607007752</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.844143989470098</v>
+        <v>2.738761032935491</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.273799957066362</v>
+        <v>-4.369030145716417</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.244521623747145</v>
+        <v>1.206429548287123</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1791006998097637</v>
+        <v>-0.3547389607007752</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.846937611001579</v>
+        <v>2.741554654466972</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.137190612972269</v>
+        <v>-4.232420801622324</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.29982770977644</v>
+        <v>1.261735634316418</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.04249135571567125</v>
+        <v>-0.2181296166066827</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.929565565849693</v>
+        <v>2.824182609315086</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.583611430391693</v>
+        <v>3.798236219360613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.279955945794919</v>
+        <v>-4.375186134444975</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.241802053387491</v>
+        <v>1.203709977927468</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1852566885383217</v>
+        <v>-0.3608949494293331</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.842986842896213</v>
+        <v>2.737603886361606</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.482044269097198</v>
+        <v>3.497956550200216</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.798047429954387</v>
+        <v>2.870567463786454</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279955945794919</v>
+        <v>-4.273148575735478</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.241802053387491</v>
+        <v>1.160951609178516</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1852566885383217</v>
+        <v>-0.3608949494293331</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.791111226940755</v>
+        <v>2.654030494128855</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240520.xlsx
+++ b/tame_output/ON/bt/strategyON_20240520.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-677.6%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.9%</t>
+          <t>445.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-588.9%</t>
+          <t>-579.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-271.4%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-108.7%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-260.1%</t>
+          <t>-241.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-304.7%</t>
+          <t>-292.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.7%</t>
+          <t>-255.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.1%</t>
+          <t>-230.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.2%</t>
+          <t>-175.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.6%</t>
+          <t>-147.6%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.04790760397142968</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.141376789387767</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.53557304922052</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.043914001645255</v>
+        <v>4.116867970907334</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1892238878783654</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.081465277145391</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.53557304922052</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.078855086142797</v>
+        <v>4.151809055404875</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1841862971507789</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.082057753621763</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.591217505486837</v>
+        <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.110819200087925</v>
+        <v>4.183773169350004</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3468123771154175</v>
+        <v>-0.2252224283452861</v>
       </c>
       <c r="E1841" t="n">
-        <v>2.995753703259645</v>
+        <v>3.044389682767698</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.428591425522199</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.991989933732879</v>
+        <v>4.064943902994957</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.4125797671648295</v>
+        <v>-0.2909898183946981</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.970464356370351</v>
+        <v>3.019100335878403</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.428591425522199</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.993007542863349</v>
+        <v>4.065961512125428</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.6178244442220742</v>
+        <v>-0.4962344954519427</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.878994517535209</v>
+        <v>2.927630497043261</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.428591425522199</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.983635574851105</v>
+        <v>4.056589544113184</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6995963446498259</v>
+        <v>-0.5780063958796944</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.836368483319346</v>
+        <v>2.885004462827399</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.455626998928335</v>
+        <v>1.577216947698467</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.989939644850025</v>
+        <v>4.062893614112104</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7668054525217036</v>
+        <v>-0.6452155037515721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.814250157004297</v>
+        <v>2.86288613651235</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.455626998928335</v>
+        <v>1.577216947698467</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.994704961683727</v>
+        <v>4.067658930945806</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9743712369133155</v>
+        <v>-0.852781288143184</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.729048639366892</v>
+        <v>2.777684618874945</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.248061214536723</v>
+        <v>1.369651163306855</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.867990287168</v>
+        <v>3.940944256430079</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.392125260460152</v>
+        <v>-1.270535311690021</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.559873921453221</v>
+        <v>2.608509900961274</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8303071909898864</v>
+        <v>0.9518971397600179</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.615264764544961</v>
+        <v>3.68821873380704</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.595414729781955</v>
+        <v>-1.473824781011824</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.478424350323422</v>
+        <v>2.527060329831475</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8683866017554581</v>
+        <v>0.9899765505255895</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.637978627603226</v>
+        <v>3.710932596865305</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.803418788135032</v>
+        <v>-1.681828839364901</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.400114871536116</v>
+        <v>2.448750851044169</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8683866017554581</v>
+        <v>0.9899765505255895</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.642870772157151</v>
+        <v>3.71582474141923</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.014831209023008</v>
+        <v>-1.893241260252876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.310631359518914</v>
+        <v>2.359267339026967</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.656974180867483</v>
+        <v>0.7785641296376145</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.511104775962355</v>
+        <v>3.584058745224433</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.35398958661153</v>
+        <v>-2.232399637841398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.168052307789954</v>
+        <v>2.216688287298007</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.317815803278961</v>
+        <v>0.4394057520490924</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.300694048715691</v>
+        <v>3.373648017977769</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.562480368063214</v>
+        <v>-2.440890419293083</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.104994284948049</v>
+        <v>2.153630264456102</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1093250218272765</v>
+        <v>0.230914970597408</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.195937869583448</v>
+        <v>3.268891838845527</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.809681552828436</v>
+        <v>-2.688091604058305</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.014212561450529</v>
+        <v>2.062848540958581</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.129478375326089</v>
+        <v>0.2510683240962204</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.216128632091304</v>
+        <v>3.289082601353383</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.302066580852533</v>
+        <v>-3.180476632082402</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.818364942284622</v>
+        <v>1.867000921792675</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3629066526980078</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.921804007320578</v>
+        <v>2.994757976582657</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.687246971782605</v>
+        <v>-3.565657023012474</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.662835324725457</v>
+        <v>1.711471304233509</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3629066526980078</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.920346546133441</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.030929745009268</v>
+        <v>-3.909339796239137</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.527131338889408</v>
+        <v>1.57576731839746</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.470812704725226</v>
+        <v>-0.3492227559550946</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.857372038371727</v>
+        <v>2.930326007633806</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.237441521896289</v>
+        <v>-4.115851573126158</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.440632686790857</v>
+        <v>1.489268666298909</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6773244816122475</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.729571030895772</v>
+        <v>2.802525000157851</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.493282607674982</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.340069179179639</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6773244816122475</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.731343957596031</v>
+        <v>2.80429792685811</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.92508840082477</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.153679749387129</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8137419780535144</v>
+        <v>-0.692152029283383</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.635826347198675</v>
+        <v>2.708780316460754</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.159782394957322</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.048086926736199</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8074057108242593</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.627912882538319</v>
+        <v>2.700866851800398</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.495445042187774</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9124024594999827</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8074057108242593</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.626493474194284</v>
+        <v>2.699447443456363</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.859071287088088</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7734395217740988</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9056273476913851</v>
+        <v>-0.7840373989212537</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.574048052308251</v>
+        <v>2.647002021570329</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.224198669726834</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6266430837244314</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.201938131990398</v>
+        <v>-1.080348183220266</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.395516096734674</v>
+        <v>2.468470065996753</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.632787446907512</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4619691168669195</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.610526909171076</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.149124374441026</v>
+        <v>2.222078343703105</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.909363547223345</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.346524109212047</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.610526909171076</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.144309806912487</v>
+        <v>2.217263776174566</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.325755421510342</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1779614101061253</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.610526909171076</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.142303857521364</v>
+        <v>2.215257826783443</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.702432432040187</v>
+        <v>-7.580842483270056</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03754929656286654</v>
+        <v>0.08618527607091897</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.610526909171076</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.152562548190043</v>
+        <v>2.225516517452122</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.048307254024996</v>
+        <v>-7.926717305254865</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1047010670853621</v>
+        <v>-0.05606508757730966</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.610526909171076</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.148662113335738</v>
+        <v>2.221616082597818</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.21188713220938</v>
+        <v>-8.090297183439249</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1717280983041145</v>
+        <v>-0.1230921187960621</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.610526909171076</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.147067033390739</v>
+        <v>2.220021002652818</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.508548474019578</v>
+        <v>-8.386958525249447</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2866136590989856</v>
+        <v>-0.2379776795909332</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.679270044904955</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.10960012787962</v>
+        <v>2.182554097141699</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.631792863235008</v>
+        <v>-8.510202914464877</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3399377193195607</v>
+        <v>-0.2913017398115083</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.679270044904955</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.105573823345217</v>
+        <v>2.178527792607296</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.014794251977639</v>
+        <v>-8.893204303207508</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4932403761381972</v>
+        <v>-0.4446043966301447</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.679270044904955</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.105471722023633</v>
+        <v>2.178425691285712</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.17219313219076</v>
+        <v>-9.050603183420629</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5536284122520154</v>
+        <v>-0.504992432743963</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.836668925118076</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.013603909867191</v>
+        <v>2.08655787912927</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.531723454694761</v>
+        <v>-9.41013350592463</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6920902379555658</v>
+        <v>-0.6434542584475134</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.836668925118076</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.018954213165241</v>
+        <v>2.09190818242732</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.582072518148983</v>
+        <v>-9.460482569378852</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7043138433800773</v>
+        <v>-0.6556778638720249</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.887017988572298</v>
+        <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.996660795049885</v>
+        <v>2.069614764311964</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.679691795570379</v>
+        <v>-9.558101846800248</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7403198037268668</v>
+        <v>-0.6916838242188144</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.984637265993695</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.941130979218816</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.676000870613969</v>
+        <v>-9.554410921843838</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7388434337443024</v>
+        <v>-0.69020745423625</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.984637265993695</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.941130979218816</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.880259045943832</v>
+        <v>-9.758669097173701</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8150335067576053</v>
+        <v>-0.7663975272495529</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.112276210607683</v>
+        <v>-1.990686261837552</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.870060809569065</v>
+        <v>1.943014778831144</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09829681757501</v>
+        <v>-9.976706868804879</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8977660609256408</v>
+        <v>-0.8491300814175879</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.287046978703582</v>
+        <v>-2.165457029933451</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.769680903195962</v>
+        <v>1.842634872458041</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.02482698590756</v>
+        <v>-9.90323703713743</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8530064267652397</v>
+        <v>-0.8043704472571873</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.213577147036134</v>
+        <v>-2.091987198266002</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.829134503689852</v>
+        <v>1.902088472951931</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.1999514032941</v>
+        <v>-10.07836145452397</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9085009729723401</v>
+        <v>-0.8598649934642877</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.388701564422678</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.738615074005442</v>
+        <v>1.811569043267521</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43440349730859</v>
+        <v>-10.31281354853846</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.009500975479732</v>
+        <v>-0.9608649959716797</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.388701564422678</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.731395909103846</v>
+        <v>1.804349878365925</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72220734184583</v>
+        <v>-10.6006173930757</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.131294704068603</v>
+        <v>-1.082658724560551</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.676505408959916</v>
+        <v>-2.554915460189784</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.552041411607527</v>
+        <v>1.624995380869606</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.77499349744616</v>
+        <v>-10.65340354867603</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.151293376470178</v>
+        <v>-1.102657396962126</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.772180895542313</v>
+        <v>-2.650590946772181</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.495751909496646</v>
+        <v>1.568705878758724</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00702241718242</v>
+        <v>-10.88543246841229</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.241411215735568</v>
+        <v>-1.192775236227515</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.834193592730736</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.461238019812706</v>
+        <v>1.534191989074785</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95500690321361</v>
+        <v>-10.83341695444348</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.216614674461642</v>
+        <v>-1.16797869495359</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.834193592730736</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.465228355499107</v>
+        <v>1.538182324761186</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09667874493773</v>
+        <v>-10.9750887961676</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.274758638050032</v>
+        <v>-1.226122658541979</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.834193592730736</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.463753128600365</v>
+        <v>1.536707097862444</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04708790051289</v>
+        <v>-10.92549795174276</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.239868890115226</v>
+        <v>-1.191232910607174</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.784602748305902</v>
+        <v>-2.663012799535771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.508561045420138</v>
+        <v>1.581515014682217</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84793579327579</v>
+        <v>-10.72634584450566</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.173259180867069</v>
+        <v>-1.124623201359017</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.619280222356089</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.594703427343343</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62209064055638</v>
+        <v>-10.50050069178625</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.073342046743096</v>
+        <v>-1.024706067235044</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.577353546768925</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.62943850573185</v>
+        <v>1.702392474993929</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49751198421879</v>
+        <v>-10.37592203544866</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.022371439652</v>
+        <v>-0.9737354601439487</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.577353546768925</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.630577650287909</v>
+        <v>1.703531619549988</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55040727226308</v>
+        <v>-10.42881732349295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.040895780707607</v>
+        <v>-0.9922598011995554</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.572398200680479</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.636184632103084</v>
+        <v>1.709138601365163</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26649854133433</v>
+        <v>-10.1449085925642</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9215985840974712</v>
+        <v>-0.8729626045894197</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.572398200680479</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.64191833634172</v>
+        <v>1.7148723056038</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19513214872468</v>
+        <v>-10.07354219995455</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9027892894474778</v>
+        <v>-0.8541533099394254</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.501031808070831</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.675000909513644</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.931295281520612</v>
+        <v>-9.809705332750482</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8071380238787573</v>
+        <v>-0.7585020443707053</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.501031808070831</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.665117428200736</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.664053480652214</v>
+        <v>-9.542463531882085</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7020758640307716</v>
+        <v>-0.6534398845227201</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.501031808070831</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.663282867701363</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.566146441975723</v>
+        <v>-9.444556493205594</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6632133635336364</v>
+        <v>-0.6145773840255848</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.433046058210275</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.703774002644236</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.542192900999765</v>
+        <v>-9.420602952229636</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6529634409977594</v>
+        <v>-0.6043274614897078</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.409092517234317</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.718814633375304</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.278132962676969</v>
+        <v>-9.156543013906839</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5605997818303932</v>
+        <v>-0.5119638023223412</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.145032578911521</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.863990280207229</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.571053339172131</v>
+        <v>-8.449463390402002</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2805549660887587</v>
+        <v>-0.2319189865807072</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.145032578911521</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.861203246546928</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.530869040805941</v>
+        <v>-8.409279092035812</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2641376228544412</v>
+        <v>-0.2155016433463897</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.104848280545331</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.885657449454484</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450799245268136</v>
+        <v>-8.329209296498007</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2327428834185628</v>
+        <v>-0.1841069039105108</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.024778485007527</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933066147997923</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.217318023038537</v>
+        <v>-8.095728074268408</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1314259656888703</v>
+        <v>-0.08278998618081879</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.791297262777928</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.081079310173535</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067651632031023</v>
+        <v>-7.946061683260893</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07445161959882407</v>
+        <v>-0.02581564009077209</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.698393771535392</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.133929194606098</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.935376158400136</v>
+        <v>-7.813786209630006</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02617394339944257</v>
+        <v>0.02246203610860986</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.566118297904505</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.208661965531657</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.862793171524056</v>
+        <v>-7.623186534956853</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.00567431203862645</v>
+        <v>0.1015169666655074</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.493535311028426</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.255026818344941</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.613793372840475</v>
+        <v>-7.374186736273272</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1181805727357177</v>
+        <v>0.2140232273625986</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.493535311028426</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.2679331595686</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.71938336261358</v>
+        <v>-7.479776726046377</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05203135277274296</v>
+        <v>0.04381130185413795</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.59912530080153</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.076603236105519</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.738118264732177</v>
+        <v>-7.498511628164974</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01098097174309531</v>
+        <v>0.08486168288378559</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.59912530080153</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.125147577982605</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.590178223324577</v>
+        <v>-7.350571586757375</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07168387786822317</v>
+        <v>0.02415877675865774</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.578804384892972</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.017461204839572</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.565949586935605</v>
+        <v>-7.326342950368402</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07070640956611252</v>
+        <v>0.02513624506076884</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.554575748504</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.023284400419477</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.522401180164914</v>
+        <v>-7.282794543597712</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06024765895292949</v>
+        <v>0.03559499567395186</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.554575748504</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.016323788324384</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.280252786711056</v>
+        <v>-7.040646150143854</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05107405280975685</v>
+        <v>0.1469167074366382</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.554575748504</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.030786142705527</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.217023414942708</v>
+        <v>-6.977416778375505</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0708979219762913</v>
+        <v>0.1667405766031722</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.554575748504</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.025318263164722</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.093732280125577</v>
+        <v>-6.854125643558374</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1177124699137204</v>
+        <v>0.2135551245406018</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.43128461368687</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.096791038065577</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.072583081222134</v>
+        <v>-6.832976444654931</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1338731277124232</v>
+        <v>0.2297157823393041</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.410135414783426</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.117181535644968</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.828817639238689</v>
+        <v>-6.589211002671487</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2271600128528513</v>
+        <v>0.3230026674797326</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.410135414783426</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.112962243992019</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.68192061152082</v>
+        <v>-6.442313974953617</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2880431378600155</v>
+        <v>0.3838857924868964</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.362477172804838</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.143681503099188</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.432070217571745</v>
+        <v>-6.192463581004542</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3807253704233475</v>
+        <v>0.4765680250502284</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.362477172804838</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.13642357808289</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.256178125104313</v>
+        <v>-6.01657148853711</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4546813309309687</v>
+        <v>0.5505239855578501</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.362477172804838</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.140022701603539</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.084731662081849</v>
+        <v>-5.845125025514647</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5365874221945082</v>
+        <v>0.6324300768213891</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.191030709782375</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.25621808547157</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.859698662413027</v>
+        <v>-5.620092025845824</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6256210996783342</v>
+        <v>0.7214637543052151</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9659977101135523</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.390258362889161</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.796062920179092</v>
+        <v>-5.556456283611889</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6557701976262251</v>
+        <v>0.7516128522531065</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9023619678796178</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.433134609283839</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.703062878973194</v>
+        <v>-5.463456242405991</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6741644728923801</v>
+        <v>0.7700071275192615</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9023619678796178</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.414328868067635</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.462632382168334</v>
+        <v>-5.223025745601131</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7720797482392019</v>
+        <v>0.8679224028660828</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6619314710747575</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.560330242775428</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.390389813997139</v>
+        <v>-5.150783177429936</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8049060893425</v>
+        <v>0.9007487439693809</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6619314710747575</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.564259556610248</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349963</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.274449964371954</v>
+        <v>-5.034843327804751</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.851960613109914</v>
+        <v>0.9478032677367949</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5851097400586336</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.611031179137263</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.165645078892227</v>
+        <v>-4.926038442325024</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.892480638521798</v>
+        <v>0.9883232931486794</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5851097400586336</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.608029250357256</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.945624280855216</v>
+        <v>-4.706017644288013</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9820679947472166</v>
+        <v>1.077910649374098</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4438898949906533</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694340194408658</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.812756591791938</v>
+        <v>-4.573149955224736</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.051109253174351</v>
+        <v>1.146951907801232</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4438898949906533</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.710234377210482</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.653241488272569</v>
+        <v>-4.413634851705366</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.116061139022401</v>
+        <v>1.211903793649282</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2843747914712834</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.807089283762406</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.508569343172831</v>
+        <v>-4.268962706605628</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.184018099623735</v>
+        <v>1.279860754250617</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.139702646371546</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.903980673383688</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.568444170530523</v>
+        <v>-4.328837533963321</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.146105660082084</v>
+        <v>1.241948314708966</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1995774737292381</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.854093268370498</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.481644672751514</v>
+        <v>-4.344424163936356</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.203225952516254</v>
+        <v>1.258114156042317</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1995774737292381</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.876493761693065</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.48411437921332</v>
+        <v>-4.346893870398162</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.202310471304944</v>
+        <v>1.257198674831007</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2020471801910443</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.875084339189393</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.55248456553733</v>
+        <v>-4.415264056722172</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.185969319250042</v>
+        <v>1.240857522776105</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1927714811548293</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.891656681085824</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.431068135910854</v>
+        <v>-4.293847627095696</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.224972599732524</v>
+        <v>1.279860803258587</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1927714811548293</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.882093389717715</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.462061295239559</v>
+        <v>-4.324840786424401</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.037284901041428</v>
+        <v>1.092173104567492</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1927714811548293</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.706802954758102</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.28658703544709</v>
+        <v>-4.149366526631932</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.112041836950204</v>
+        <v>1.166930040476267</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1927714811548293</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.71137018674989</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.397523288088339</v>
+        <v>-4.26030277927318</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.043409364654912</v>
+        <v>1.098297568180975</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1927714811548293</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.687112215511097</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.600549865631572</v>
+        <v>-4.463329356816414</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9653301188575238</v>
+        <v>1.020218322383587</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3957980586980627</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.568427654205062</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.442624266696279</v>
+        <v>-4.305403757881121</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.038672744863773</v>
+        <v>1.093560948389837</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3957980586980627</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.578600040637195</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.356380803669901</v>
+        <v>-4.219160294854743</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.068116400648185</v>
+        <v>1.123004604174248</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3957980586980627</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.573546311211055</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.357563888320962</v>
+        <v>-4.220343379505804</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.059418942232286</v>
+        <v>1.114307145758349</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4014411071645743</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.561936257575674</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.234436181326879</v>
+        <v>-4.097215672511721</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.109221898063021</v>
+        <v>1.164110101589084</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4014411071645743</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.562488130608775</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.14162569987602</v>
+        <v>-4.004405191060862</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.07561878253473</v>
+        <v>1.130506986060793</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3086306257137149</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.547447111370657</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.09306264765499</v>
+        <v>-4.023975114086307</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.096917479347743</v>
+        <v>1.124552492775216</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2600675734926847</v>
+        <v>-0.08859391217195439</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.578458418627875</v>
+        <v>2.681342615420314</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.98039142941874</v>
+        <v>-3.911303895850057</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.137061675153966</v>
+        <v>1.164696688581439</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1473963552564345</v>
+        <v>0.02407730606429581</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.641136858081349</v>
+        <v>2.744021054873787</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.868014428236067</v>
+        <v>-3.798926894667384</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.187503771457702</v>
+        <v>1.215138784885176</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1473963552564345</v>
+        <v>0.02407730606429581</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.646628153912016</v>
+        <v>2.749512350704454</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.066248997122798</v>
+        <v>-3.997161463554114</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.119707145671549</v>
+        <v>1.147342159099022</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3456309241431651</v>
+        <v>-0.1741572628224348</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.539184614348517</v>
+        <v>2.642068811140955</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.149250278148076</v>
+        <v>-4.080162744579393</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9248623532620908</v>
+        <v>0.9524973666895642</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3642018086703389</v>
+        <v>-0.1927281473496085</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.366397803632866</v>
+        <v>2.469282000425304</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.9900560060915</v>
+        <v>-3.920968472522817</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.108689722803927</v>
+        <v>1.1363247362314</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3642018086703389</v>
+        <v>-0.1927281473496085</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.486547464352071</v>
+        <v>2.58943166114451</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.076654589072604</v>
+        <v>-4.00756705550392</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.088563315713809</v>
+        <v>1.116198329141282</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3642018086703389</v>
+        <v>-0.1927281473496085</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.501060490454394</v>
+        <v>2.603944687246833</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.038270926514453</v>
+        <v>-3.969183392945768</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.101336222079438</v>
+        <v>1.128971235506911</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3258181461121877</v>
+        <v>-0.1543444847914573</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.521510129331654</v>
+        <v>2.624394326124092</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.861154596479286</v>
+        <v>-3.792067062910602</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.168911782938806</v>
+        <v>1.196546796366279</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3258181461121877</v>
+        <v>-0.1543444847914573</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.518239158176955</v>
+        <v>2.621123354969394</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.831452472502993</v>
+        <v>-3.762364938934309</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.181476024291237</v>
+        <v>1.20911103771871</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.330288271327501</v>
+        <v>-0.1588146100067707</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.516240474809681</v>
+        <v>2.619124671602119</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.652077051264225</v>
+        <v>-3.582989517695541</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.247013168093158</v>
+        <v>1.274648181520632</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1735115131567824</v>
+        <v>-0.00203785183605204</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.604093505018526</v>
+        <v>2.706977701810965</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.716988143452227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.697091264784831</v>
+        <v>-3.628003731216147</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.209814938016505</v>
+        <v>1.237449951443979</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.203860408471387</v>
+        <v>-0.03238674715065665</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.566691623161353</v>
+        <v>2.669575819953792</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.964095775057267</v>
+        <v>-3.895008241488582</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.108704696246477</v>
+        <v>1.13633970967395</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3982234465143356</v>
+        <v>-0.2267497851936052</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.45576536267453</v>
+        <v>2.558649559466968</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.252882995516182</v>
+        <v>-4.183795461947497</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9923937299594123</v>
+        <v>1.020028743386886</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4993095666133359</v>
+        <v>-0.3278359052926056</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.394317612511631</v>
+        <v>2.497201809304069</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.22040740934541</v>
+        <v>-4.151319875776725</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.002983925982038</v>
+        <v>1.030618939409512</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4993095666133359</v>
+        <v>-0.3278359052926056</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.391917574065948</v>
+        <v>2.494801770858386</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.201369281638113</v>
+        <v>-4.132281748069428</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.007123896273202</v>
+        <v>1.034758909700675</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5574931779445305</v>
+        <v>-0.3860195166238001</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.353532126475476</v>
+        <v>2.456416323267914</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.218115146894488</v>
+        <v>-4.149027613325803</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.178007419109332</v>
+        <v>1.205642432536806</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5574931779445305</v>
+        <v>-0.3860195166238001</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.531113995414156</v>
+        <v>2.633998192206595</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.270435527495279</v>
+        <v>-4.201347993926595</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.157912595855149</v>
+        <v>1.185547609282623</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5225463179356583</v>
+        <v>-0.351072656614928</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.552915440405613</v>
+        <v>2.655799637198052</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.414758433420198</v>
+        <v>-4.345670899851513</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.106191963882107</v>
+        <v>1.133826977309581</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5225463179356583</v>
+        <v>-0.351072656614928</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.558923970802539</v>
+        <v>2.661808167594978</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.267015463185196</v>
+        <v>-4.197927929616511</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.24444179976813</v>
+        <v>1.272076813195604</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3547389607007752</v>
+        <v>-0.1832652993800448</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.738761032935491</v>
+        <v>2.841645229727929</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651169</v>
+        <v>3.802242353651168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.369030145716417</v>
+        <v>-4.299942612147732</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.206429548287123</v>
+        <v>1.234064561714596</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3547389607007752</v>
+        <v>-0.1832652993800448</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.741554654466972</v>
+        <v>2.84443885125941</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864729</v>
+        <v>3.805605409864727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.232420801622324</v>
+        <v>-4.163333268053639</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.261735634316418</v>
+        <v>1.289370647743892</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2181296166066827</v>
+        <v>-0.04665595528595234</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.824182609315086</v>
+        <v>2.927066806107524</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360613</v>
+        <v>3.798236219360612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.375186134444975</v>
+        <v>-4.30609860087629</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.203709977927468</v>
+        <v>1.231344991354942</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3608949494293331</v>
+        <v>-0.1894212881086028</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.737603886361606</v>
+        <v>2.840488083154044</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.497956550200216</v>
+        <v>3.5593009389168</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.870567463786454</v>
+        <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.273148575735478</v>
+        <v>-4.178233919969297</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.160951609178516</v>
+        <v>1.34882641751456</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3608949494293331</v>
+        <v>-0.0606899575535545</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.654030494128855</v>
+        <v>2.984062435283894</v>
       </c>
     </row>
   </sheetData>
